--- a/CFI_Master_Excel.xlsx
+++ b/CFI_Master_Excel.xlsx
@@ -435,212 +435,242 @@
     <author>CFI System</author>
   </authors>
   <commentList>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="D12" authorId="0" shapeId="0">
+      <text>
+        <t>No verified data for POS S%</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PMF S%</t>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
+    <comment ref="G12" authorId="0" shapeId="0">
       <text>
         <t>No verified data for POME S%</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0">
+    <comment ref="H12" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PKS S%</t>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0">
+    <comment ref="I12" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PPF S%</t>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0">
+    <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Trunk S%</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0">
+    <comment ref="K12" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Frond S%</t>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="L12" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Sludge S%</t>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0">
+    <comment ref="D13" authorId="0" shapeId="0">
+      <text>
+        <t>No verified data for POS Fe_ppm</t>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PMF Fe_ppm</t>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
+    <comment ref="G13" authorId="0" shapeId="0">
       <text>
         <t>No verified data for POME Fe_ppm</t>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0">
+    <comment ref="H13" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PKS Fe_ppm</t>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PPF Fe_ppm</t>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Trunk Fe_ppm</t>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0">
+    <comment ref="K13" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Frond Fe_ppm</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0">
+    <comment ref="L13" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Sludge Fe_ppm</t>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0">
+    <comment ref="D14" authorId="0" shapeId="0">
+      <text>
+        <t>No verified data for POS Zn_ppm</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PMF Zn_ppm</t>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0">
+    <comment ref="G14" authorId="0" shapeId="0">
       <text>
         <t>No verified data for POME Zn_ppm</t>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PKS Zn_ppm</t>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="I14" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PPF Zn_ppm</t>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0">
+    <comment ref="J14" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Trunk Zn_ppm</t>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0">
+    <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Frond Zn_ppm</t>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0">
+    <comment ref="L14" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Sludge Zn_ppm</t>
       </text>
     </comment>
-    <comment ref="E15" authorId="0" shapeId="0">
+    <comment ref="D15" authorId="0" shapeId="0">
+      <text>
+        <t>No verified data for POS Cu_ppm</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PMF Cu_ppm</t>
       </text>
     </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
+    <comment ref="G15" authorId="0" shapeId="0">
       <text>
         <t>No verified data for POME Cu_ppm</t>
       </text>
     </comment>
-    <comment ref="G15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PKS Cu_ppm</t>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="I15" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PPF Cu_ppm</t>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Trunk Cu_ppm</t>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="K15" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Frond Cu_ppm</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0">
+    <comment ref="L15" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Sludge Cu_ppm</t>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0">
+    <comment ref="D16" authorId="0" shapeId="0">
+      <text>
+        <t>No verified data for POS Mn_ppm</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PMF Mn_ppm</t>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
+    <comment ref="G16" authorId="0" shapeId="0">
       <text>
         <t>No verified data for POME Mn_ppm</t>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0">
+    <comment ref="H16" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PKS Mn_ppm</t>
       </text>
     </comment>
-    <comment ref="H16" authorId="0" shapeId="0">
+    <comment ref="I16" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PPF Mn_ppm</t>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0">
+    <comment ref="J16" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Trunk Mn_ppm</t>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0">
+    <comment ref="K16" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Frond Mn_ppm</t>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0">
+    <comment ref="L16" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Sludge Mn_ppm</t>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="D17" authorId="0" shapeId="0">
+      <text>
+        <t>No verified data for POS B_ppm</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PMF B_ppm</t>
       </text>
     </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
+    <comment ref="G17" authorId="0" shapeId="0">
       <text>
         <t>No verified data for POME B_ppm</t>
       </text>
     </comment>
-    <comment ref="G17" authorId="0" shapeId="0">
+    <comment ref="H17" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PKS B_ppm</t>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0">
+    <comment ref="I17" authorId="0" shapeId="0">
       <text>
         <t>No verified data for PPF B_ppm</t>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0">
+    <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Trunk B_ppm</t>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0">
+    <comment ref="K17" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Frond B_ppm</t>
       </text>
     </comment>
-    <comment ref="K17" authorId="0" shapeId="0">
+    <comment ref="L17" authorId="0" shapeId="0">
       <text>
         <t>No verified data for Sludge B_ppm</t>
       </text>
@@ -1514,7 +1544,7 @@
   </mergeCells>
   <dataValidations count="8">
     <dataValidation sqref="D11 D12 D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Select a valid residue" type="list">
-      <formula1>"EFB,OPDC,PKSA,PMF,POME,PKS,PPF,Trunk,Frond,Sludge"</formula1>
+      <formula1>"EFB,OPDC,POS,PKSA,PMF,POME,PKS,PPF,Trunk,Frond,Sludge"</formula1>
     </dataValidation>
     <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Select a valid chemical" type="list">
       <formula1>"PKSA,CaCO3,H2O2,Urea,Lime Ca(OH)2,MgSO4,NPK 15-15-15,Molasses,PKSA+CaCO3,PKSA+H2O2+Urea,NaOH"</formula1>
@@ -1537,7 +1567,7 @@
       <formula1>"None,FSSC 22000,ISO 22716"</formula1>
     </dataValidation>
     <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Inceptisols,Ultisols,Oxisols,Histosols,Spodosols,All"</formula1>
+      <formula1>"Inceptisols,Ultisols,Oxisols,Histosols,Spodosols,Andisols,All"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3995,7 +4025,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Best fertility, standard reference</t>
+          <t>Best fertility, standard reference. Phanerochaete 4.8 star top performer.</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4061,7 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Standard NPK baseline for fertiliser calcs</t>
+          <t>Standard NPK baseline. Aspergillus 4.5 star top performer.</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4097,7 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Fe/Al oxide-dominant, low CEC, high P fixation</t>
+          <t>Fe/Al oxide-dominant, P-fixation 65%. Aspergillus 4.8 star top.</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4133,7 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>Peat/organic, C=24.5%, very high OM</t>
+          <t>Peat/organic, C=24.5%. CRITICAL Cu/Zn deficiency. Lactobacillus 4.2 star top.</t>
         </is>
       </c>
     </row>
@@ -4140,6 +4170,42 @@
       <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Sandy, lowest fertility, ~31% lower yield vs Ultisols</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Andisols</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Volcanic, P-fixation 82% HIGHEST, allophane minerals</t>
         </is>
       </c>
     </row>
@@ -4401,6 +4467,28 @@
       </c>
       <c r="F24" s="41" t="n">
         <v>124.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Andisols</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="41" t="n">
+        <v>106.8</v>
       </c>
     </row>
     <row r="26">
@@ -4454,10 +4542,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
@@ -4466,19 +4554,18 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>CAPEX &amp; OPEX ANALYSIS</t>
+          <t>CAPEX &amp; OPEX ANALYSIS — FULL ENGINEERING BUILD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>CAPITAL EXPENDITURE (CAPEX)</t>
+          <t>S1 — EFB PROCESSING LINE (20 t/h, 153kW nameplate)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -4500,52 +4587,52 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Stage 1 — Shredder (EFB)</t>
+          <t>RCV-EFB-01 — EFB Receiving Hopper (50m3, hydraulic gate)</t>
         </is>
       </c>
       <c r="B5" s="46" t="n">
-        <v>85000</v>
+        <v>28000</v>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Stage 1 — Hammer mill</t>
+          <t>CVB-EFB-01 — Drag Chain Conveyor (12m x 600mm, VFD, 7.5kW)</t>
         </is>
       </c>
       <c r="B6" s="46" t="n">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Stage 1 — Mixing tank + conveyor</t>
+          <t>ESD-01 — Primary Twin-Shaft Shredder (2x37kW = 74kW, 15-25 RPM)</t>
         </is>
       </c>
       <c r="B7" s="46" t="n">
-        <v>35000</v>
+        <v>95000</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Stage 1 — PKSA soaking vessel</t>
+          <t>CVB-EFB-02 — Incline Belt Conveyor (8m x 600mm, 30deg, 5.5kW)</t>
         </is>
       </c>
       <c r="B8" s="46" t="n">
@@ -4553,29 +4640,29 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Stage 2 — Chemical dosing system</t>
+          <t>BIN-EFB-01 — Buffer Bin (50m3, VFD screw feeder, 2.5hr cap)</t>
         </is>
       </c>
       <c r="B9" s="46" t="n">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Stage 2 — Neutralisation tank</t>
+          <t>ELB-01 — Lump Breaker twin-roller (30-50mm gap, 11kW)</t>
         </is>
       </c>
       <c r="B10" s="46" t="n">
@@ -4583,463 +4670,1476 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Stage 3 — Biological inoculation system</t>
+          <t>EHM-01 — Hammer Mill (2mm screen, 37kW nameplate/24kW derated)</t>
         </is>
       </c>
       <c r="B11" s="46" t="n">
-        <v>18000</v>
+        <v>65000</v>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Stage 3 — Composting area (covered)</t>
+          <t>ESC-01 — Vibrating Screen linear (2mm mesh, 2x1.5kW)</t>
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Stage 4 — BSF rearing shed (per 500m2)</t>
+          <t>EPR-01 — Screw Press twin-screw (62.5%-&gt;45-50% MC, 15kW)</t>
         </is>
       </c>
       <c r="B13" s="46" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Stage 4</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Stage 4 — BSF neonate nursery</t>
+          <t>BIN-EFB-301 — S2 Buffer Bin (50m3, 2.5hr)</t>
         </is>
       </c>
       <c r="B14" s="46" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Stage 4</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Stage 4 — Climate control system</t>
+          <t>EDC-01 — Baghouse Dust Collection</t>
         </is>
       </c>
       <c r="B15" s="46" t="n">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Stage 4</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5A — Frass screening/bagging</t>
-        </is>
-      </c>
-      <c r="B16" s="46" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5B — Larvae separation equipment</t>
-        </is>
-      </c>
-      <c r="B17" s="46" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5B</t>
-        </is>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>S1 EFB Subtotal</t>
+        </is>
+      </c>
+      <c r="B16" s="22">
+        <f>SUM(B5:B15)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5B — Oil press</t>
-        </is>
-      </c>
-      <c r="B18" s="46" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5B</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>S1 — OPDC PROCESSING LINE (5 t/h, 96.2kW nameplate)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5B — Drying system</t>
-        </is>
-      </c>
-      <c r="B19" s="46" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Stage 5B</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Utilities — Water treatment</t>
+          <t>RCV-OPDC-01 — OPDC Receiving Hopper (20m3, hydraulic gate)</t>
         </is>
       </c>
       <c r="B20" s="46" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Utilities — Electrical infrastructure</t>
+          <t>CVB-OPDC-01 — Drag Chain Conveyor (10m x 500mm, VFD, 5.5kW)</t>
         </is>
       </c>
       <c r="B21" s="46" t="n">
-        <v>30000</v>
+        <v>14000</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Laboratory — Basic QC lab</t>
+          <t>OSD-01 — Primary Twin-Shaft Shredder (2x22kW = 44kW, 15-25 RPM)</t>
         </is>
       </c>
       <c r="B22" s="46" t="n">
-        <v>35000</v>
+        <v>72000</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>TOTAL CAPEX</t>
-        </is>
-      </c>
-      <c r="B23" s="51">
-        <f>IFERROR(SUM(B5:B22),0)</f>
-        <v/>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>CVB-OPDC-02 — Incline Belt Conveyor (7m x 500mm, 30deg, 4kW)</t>
+        </is>
+      </c>
+      <c r="B23" s="46" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>BIN-OPDC-01 — Buffer Bin (20m3, VFD screw feeder, 4hr cap)</t>
+        </is>
+      </c>
+      <c r="B24" s="46" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>OLB-01 — Lump Breaker twin-roller (25-40mm gap, 7.5kW)</t>
+        </is>
+      </c>
+      <c r="B25" s="46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Cost Item</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Monthly Cost (USD)</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>OHM-01 — Hammer Mill (2mm screen, 22kW nameplate/14kW derated)</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Chemical Treatment</t>
-        </is>
-      </c>
-      <c r="B27" s="22">
-        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 2</t>
+          <t>OSC-01 — Vibrating Screen linear (2mm mesh, 2x1.1kW)</t>
+        </is>
+      </c>
+      <c r="B27" s="46" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Biological Treatment</t>
-        </is>
-      </c>
-      <c r="B28" s="22">
-        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 3</t>
+          <t>OPR-01 — Screw Press twin-screw (70-75%-&gt;60-62% MC, 11kW)</t>
+        </is>
+      </c>
+      <c r="B28" s="46" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>BSF Neonates</t>
-        </is>
-      </c>
-      <c r="B29" s="22">
-        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
-        <v/>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 4</t>
+          <t>BIN-OPDC-301 — S2 Buffer Bin (15m3 concrete/carbon steel)</t>
+        </is>
+      </c>
+      <c r="B29" s="46" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Processing (S5B)</t>
-        </is>
-      </c>
-      <c r="B30" s="22">
-        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
-        <v/>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 5B</t>
+          <t>ODC-01 — Baghouse Dust Collection</t>
+        </is>
+      </c>
+      <c r="B30" s="46" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Energy / Utilities</t>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>S1 OPDC Subtotal</t>
         </is>
       </c>
       <c r="B31" s="22">
-        <f>IFERROR(S1_Preprocessing!B30,0)</f>
-        <v/>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Labour (estimated)</t>
-        </is>
-      </c>
-      <c r="B32" s="46" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>10 workers @ $800/month</t>
-        </is>
+        <f>SUM(B20:B30)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Maintenance (2% CAPEX/month)</t>
-        </is>
-      </c>
-      <c r="B33" s="22">
-        <f>IFERROR(B23*0.02/12,0)</f>
-        <v/>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Industry standard</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>S1 — POS PROCESSING LINE (1.25 t/h, 20.2kW)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Quality Control / Lab</t>
-        </is>
-      </c>
-      <c r="B34" s="46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Monthly QC testing</t>
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
+          <t>PIT-POS-01 — POS Reception Pit (15m3, RC concrete, epoxy-coated)</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>S1-POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>T-SLD-101 — Sludge Holding Tank (5-8m3, SS304, sealed dome, 3.7kW agitator)</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>S1-POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>PMP-POS-01 — Sludge Transfer Pump (progressive cavity, SS316L, 5.5kW, VFD)</t>
+        </is>
+      </c>
+      <c r="B37" s="46" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>S1-POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>DCN-POS-01 — Decanter Centrifuge 3-phase (1.5t/h, Alfa Laval, 11kW)</t>
+        </is>
+      </c>
+      <c r="B38" s="46" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>S1-POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>BUF-POS-01 — S2 Buffer Bin (5m3, carbon steel + epoxy)</t>
+        </is>
+      </c>
+      <c r="B39" s="46" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>S1-POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>S1 POS Subtotal</t>
+        </is>
+      </c>
+      <c r="B40" s="22">
+        <f>SUM(B35:B39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>S2 CHEMICAL + S3 BIOLOGICAL — HANDOFF EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>S2 Chemical Mixing Tank (covered, 20m3, paddle mixer, 15kW)</t>
+        </is>
+      </c>
+      <c r="B44" s="46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>S2 pH Monitoring Station (inline pH probe + datalogger)</t>
+        </is>
+      </c>
+      <c r="B45" s="46" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>S2 Neutralisation Bays (3x concrete bays, 50m3 each)</t>
+        </is>
+      </c>
+      <c r="B46" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3 Transfer Conveyor (covered belt, 15m, 5.5kW)</t>
+        </is>
+      </c>
+      <c r="B47" s="46" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>S3 Biological Inoculation System (spray boom + tank)</t>
+        </is>
+      </c>
+      <c r="B48" s="46" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>S3 Composting Bays (covered, 5x 100m2 windrow bays)</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>S3 Aeration System (forced air + temperature probes)</t>
+        </is>
+      </c>
+      <c r="B50" s="46" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>S3 Turning Machine (windrow turner, 22kW)</t>
+        </is>
+      </c>
+      <c r="B51" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>S2-S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>S2-S3 Subtotal</t>
+        </is>
+      </c>
+      <c r="B52" s="22">
+        <f>SUM(B44:B51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>BSF GREENHOUSE + IoT + AUTOMATION (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse Structure — Steel frame, poly-carbonate panels (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B56" s="46" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse Foundation — Concrete slab + drainage (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B57" s="46" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Internal Partition Walls — BSF zone separation (40 bays x 500m2)</t>
+        </is>
+      </c>
+      <c r="B58" s="46" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Rearing Tray System — Stacked 3-tier racks (20,000 m2 effective)</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="n">
+        <v>350000</v>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Blackout System — UV-blocking curtains + light baffles</t>
+        </is>
+      </c>
+      <c r="B60" s="46" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>HVAC System — Evaporative cooling + exhaust fans (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B61" s="46" t="n">
+        <v>280000</v>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Heating System — Hot water pipes from mill waste heat</t>
+        </is>
+      </c>
+      <c r="B62" s="46" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Humidification System — Fogging nozzles + RH control</t>
+        </is>
+      </c>
+      <c r="B63" s="46" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Air Circulation Fans — 120 units, ceiling mount</t>
+        </is>
+      </c>
+      <c r="B64" s="46" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>IoT Temperature Sensors — 200 units (5 per bay, wireless)</t>
+        </is>
+      </c>
+      <c r="B65" s="46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>IoT Humidity Sensors — 200 units (5 per bay, wireless)</t>
+        </is>
+      </c>
+      <c r="B66" s="46" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>IoT CO2 Sensors — 40 units (1 per bay)</t>
+        </is>
+      </c>
+      <c r="B67" s="46" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>IoT pH Sensors — substrate monitoring, 80 units</t>
+        </is>
+      </c>
+      <c r="B68" s="46" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>IoT Weight Sensors — tray scales for yield tracking, 200 units</t>
+        </is>
+      </c>
+      <c r="B69" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>IoT Ammonia Sensors — 40 units (1 per bay)</t>
+        </is>
+      </c>
+      <c r="B70" s="46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Central IoT Gateway — LoRaWAN/WiFi hub + cloud dashboard</t>
+        </is>
+      </c>
+      <c r="B71" s="46" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>IoT Software Platform — Dashboard, alerts, analytics (annual license)</t>
+        </is>
+      </c>
+      <c r="B72" s="46" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>Automated Feed Distribution System — conveyor + metering</t>
+        </is>
+      </c>
+      <c r="B73" s="46" t="n">
+        <v>180000</v>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Automated Larvae Harvesting System — vibrating separator + conveyor</t>
+        </is>
+      </c>
+      <c r="B74" s="46" t="n">
+        <v>220000</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Automated Tray Washing Station</t>
+        </is>
+      </c>
+      <c r="B75" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Automated Climate Control PLC — Siemens/Allen-Bradley</t>
+        </is>
+      </c>
+      <c r="B76" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>SCADA System — Central control room, 4 screens</t>
+        </is>
+      </c>
+      <c r="B77" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Water Supply System — treatment + distribution (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B78" s="46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Electrical Distribution — panels, cabling, backup genset</t>
+        </is>
+      </c>
+      <c r="B79" s="46" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Waste Water Treatment — effluent from rearing</t>
+        </is>
+      </c>
+      <c r="B80" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Fire Suppression System</t>
+        </is>
+      </c>
+      <c r="B81" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Site Clearing &amp; Grading (2.5 ha total footprint)</t>
+        </is>
+      </c>
+      <c r="B82" s="46" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Access Roads — Internal + connection to mill (500m gravel)</t>
+        </is>
+      </c>
+      <c r="B83" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Perimeter Fencing + Security</t>
+        </is>
+      </c>
+      <c r="B84" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Drainage System — Surface + subsurface</t>
+        </is>
+      </c>
+      <c r="B85" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Landscaping + Erosion Control</t>
+        </is>
+      </c>
+      <c r="B86" s="46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Staff Facilities — Office, changing rooms, canteen</t>
+        </is>
+      </c>
+      <c r="B87" s="46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Storage Warehouse — Finished product (500 m2)</t>
+        </is>
+      </c>
+      <c r="B88" s="46" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Greenhouse + IoT Subtotal</t>
+        </is>
+      </c>
+      <c r="B89" s="22">
+        <f>SUM(B56:B88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>S5 EXTRACTION &amp; POST-PROCESSING</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n"/>
+      <c r="C91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>S5A — Frass screening/bagging line</t>
+        </is>
+      </c>
+      <c r="B92" s="46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>S5B — Larvae separation (vibrating + thermal)</t>
+        </is>
+      </c>
+      <c r="B93" s="46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>S5B — Oil press (screw type, 85% eff)</t>
+        </is>
+      </c>
+      <c r="B94" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>S5B — Drying system (belt dryer)</t>
+        </is>
+      </c>
+      <c r="B95" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Laboratory — QC lab (ICP-OES capable)</t>
+        </is>
+      </c>
+      <c r="B96" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>S5 Subtotal</t>
+        </is>
+      </c>
+      <c r="B97" s="22">
+        <f>SUM(B92:B96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX SUMMARY</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n"/>
+      <c r="C99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX</t>
+        </is>
+      </c>
+      <c r="B100" s="51">
+        <f>IFERROR(SUM(B5:B99),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>Cost Item</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>Chemical Treatment</t>
+        </is>
+      </c>
+      <c r="B104" s="22">
+        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
+        <v/>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>Biological Treatment</t>
+        </is>
+      </c>
+      <c r="B105" s="22">
+        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
+        <v/>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>BSF Neonates</t>
+        </is>
+      </c>
+      <c r="B106" s="22">
+        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
+        <v/>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>Processing (S5B)</t>
+        </is>
+      </c>
+      <c r="B107" s="22">
+        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
+        <v/>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>Energy / Utilities</t>
+        </is>
+      </c>
+      <c r="B108" s="22">
+        <f>IFERROR(S1_Preprocessing!B30,0)</f>
+        <v/>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Labour (estimated)</t>
+        </is>
+      </c>
+      <c r="B109" s="46" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>10 workers @ $800/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance (2% CAPEX/month)</t>
+        </is>
+      </c>
+      <c r="B110" s="22">
+        <f>IFERROR(B100*0.02/12,0)</f>
+        <v/>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Industry standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>Quality Control / Lab</t>
+        </is>
+      </c>
+      <c r="B111" s="46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Monthly QC testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
           <t>Transport / Logistics</t>
         </is>
       </c>
-      <c r="B35" s="46" t="n">
+      <c r="B112" s="46" t="n">
         <v>3000</v>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Product distribution</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="38" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="38" t="inlineStr">
         <is>
           <t>TOTAL MONTHLY OPEX</t>
         </is>
       </c>
-      <c r="B36" s="52">
-        <f>IFERROR(SUM(B27:B35),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="B113" s="52">
+        <f>IFERROR(SUM(B104:B112),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>PAYBACK &amp; NPV ANALYSIS</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="B115" s="3" t="n"/>
+      <c r="C115" s="3" t="n"/>
+      <c r="D115" s="3" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Total CAPEX</t>
         </is>
       </c>
-      <c r="B39" s="22">
-        <f>B23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="B116" s="22">
+        <f>B100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Monthly Gross Profit</t>
         </is>
       </c>
-      <c r="B40" s="22">
-        <f>IFERROR(Summary_Dashboard!B24-B36,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="B117" s="22">
+        <f>IFERROR(Summary_Dashboard!B24-B113,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="38" t="inlineStr">
         <is>
           <t>Payback Period (months)</t>
         </is>
       </c>
-      <c r="B41" s="42">
-        <f>IFERROR(B39/B40,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="B118" s="42">
+        <f>IFERROR(B116/B117,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>Payback Period (years)</t>
         </is>
       </c>
-      <c r="B42" s="13">
-        <f>IFERROR(B41/12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="B119" s="13">
+        <f>IFERROR(B118/12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>IRR Discount Rate (user-adjustable)</t>
         </is>
       </c>
-      <c r="B44" s="53" t="n">
+      <c r="B121" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>Annual Net Cash Flow</t>
         </is>
       </c>
-      <c r="B45" s="22">
-        <f>IFERROR(B40*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="B122" s="22">
+        <f>IFERROR(B117*12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>5-Year NPV (simple estimate)</t>
         </is>
       </c>
-      <c r="B46" s="30">
-        <f>IFERROR(B45/(1+B44)^1+B45/(1+B44)^2+B45/(1+B44)^3+B45/(1+B44)^4+B45/(1+B44)^5-B39,0)</f>
+      <c r="B123" s="30">
+        <f>IFERROR(B122/(1+B121)^1+B122/(1+B121)^2+B122/(1+B121)^3+B122/(1+B121)^4+B122/(1+B121)^5-B116,0)</f>
         <v/>
       </c>
     </row>
@@ -5150,7 +6250,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C5" s="12">
         <f>IFERROR(INPUTS!$B$4*B5,0)</f>
@@ -5360,7 +6460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5411,45 +6511,50 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
           <t>PKSA</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>PMF</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>POME</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>PKS</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>PPF</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Trunk</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Frond</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Sludge</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>60:40 Blend</t>
         </is>
@@ -5468,30 +6573,33 @@
         <v>30</v>
       </c>
       <c r="D4" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="17" t="n">
         <v>98</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="F4" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="G4" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="H4" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="I4" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="I4" s="17" t="n">
+      <c r="J4" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="K4" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="L4" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="L4" s="12">
+      <c r="M4" s="12">
         <f>IFERROR(B4*INPUTS!$B$9/100+C4*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5509,30 +6617,33 @@
         <v>70</v>
       </c>
       <c r="D5" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="E5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="F5" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="G5" s="17" t="n">
         <v>96</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="H5" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="I5" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="J5" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="K5" s="17" t="n">
         <v>65</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="L5" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="L5" s="12">
+      <c r="M5" s="12">
         <f>IFERROR(B5*INPUTS!$B$9/100+C5*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5550,30 +6661,33 @@
         <v>6.8</v>
       </c>
       <c r="D6" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="17" t="n">
         <v>11.2</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="F6" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="G6" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="H6" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="I6" s="17" t="n">
         <v>5.8</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="J6" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="K6" s="17" t="n">
         <v>5.6</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="L6" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="L6" s="12">
+      <c r="M6" s="12">
         <f>IFERROR(B6*INPUTS!$B$9/100+C6*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5585,36 +6699,39 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="C7" s="17" t="n">
         <v>2.45</v>
       </c>
       <c r="D7" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E7" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="F7" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="G7" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="H7" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="I7" s="17" t="n">
         <v>0.55</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="J7" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="K7" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="L7" s="17" t="n">
         <v>2.8</v>
       </c>
-      <c r="L7" s="12">
+      <c r="M7" s="12">
         <f>IFERROR(B7*INPUTS!$B$9/100+C7*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5626,36 +6743,39 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="C8" s="17" t="n">
         <v>0.43</v>
       </c>
       <c r="D8" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E8" s="17" t="n">
         <v>2.94</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="F8" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="G8" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="H8" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="I8" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="J8" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="K8" s="17" t="n">
         <v>0.12</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="L8" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="L8" s="12">
+      <c r="M8" s="12">
         <f>IFERROR(B8*INPUTS!$B$9/100+C8*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5667,36 +6787,39 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>2.2</v>
       </c>
       <c r="D9" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="17" t="n">
         <v>12.5</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="F9" s="17" t="n">
         <v>1.8</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="G9" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="H9" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="I9" s="17" t="n">
         <v>1.4</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="J9" s="17" t="n">
         <v>0.8</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="K9" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="L9" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="L9" s="12">
+      <c r="M9" s="12">
         <f>IFERROR(B9*INPUTS!$B$9/100+C9*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5714,30 +6837,33 @@
         <v>1</v>
       </c>
       <c r="D10" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E10" s="17" t="n">
         <v>8.5</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="F10" s="17" t="n">
         <v>0.35</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="G10" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="H10" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="I10" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="J10" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="K10" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="L10" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="L10" s="12">
+      <c r="M10" s="12">
         <f>IFERROR(B10*INPUTS!$B$9/100+C10*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5755,30 +6881,33 @@
         <v>0.55</v>
       </c>
       <c r="D11" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E11" s="17" t="n">
         <v>2.2</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="F11" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="G11" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="H11" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="I11" s="17" t="n">
         <v>0.12</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="J11" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="K11" s="17" t="n">
         <v>0.18</v>
       </c>
-      <c r="K11" s="17" t="n">
+      <c r="L11" s="17" t="n">
         <v>0.35</v>
       </c>
-      <c r="L11" s="12">
+      <c r="M11" s="12">
         <f>IFERROR(B11*INPUTS!$B$9/100+C11*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5795,45 +6924,50 @@
       <c r="C12" s="17" t="n">
         <v>0.18</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>DATA_GAP</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="K12" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
+      <c r="L12" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="L12" s="12">
+      <c r="M12" s="12">
         <f>IFERROR(B12*INPUTS!$B$9/100+C12*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5850,45 +6984,50 @@
       <c r="C13" s="17" t="n">
         <v>800</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>DATA_GAP</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
+      <c r="L13" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="L13" s="12">
+      <c r="M13" s="12">
         <f>IFERROR(B13*INPUTS!$B$9/100+C13*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5905,45 +7044,50 @@
       <c r="C14" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>DATA_GAP</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
+      <c r="L14" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="L14" s="12">
+      <c r="M14" s="12">
         <f>IFERROR(B14*INPUTS!$B$9/100+C14*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -5960,45 +7104,50 @@
       <c r="C15" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>DATA_GAP</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="L15" s="12">
+      <c r="M15" s="12">
         <f>IFERROR(B15*INPUTS!$B$9/100+C15*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6015,45 +7164,50 @@
       <c r="C16" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>DATA_GAP</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="K16" s="18" t="inlineStr">
+      <c r="L16" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="L16" s="12">
+      <c r="M16" s="12">
         <f>IFERROR(B16*INPUTS!$B$9/100+C16*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6070,45 +7224,50 @@
       <c r="C17" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>DATA_GAP</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="J17" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="K17" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="K17" s="18" t="inlineStr">
+      <c r="L17" s="18" t="inlineStr">
         <is>
           <t>DATA_GAP</t>
         </is>
       </c>
-      <c r="L17" s="12">
+      <c r="M17" s="12">
         <f>IFERROR(B17*INPUTS!$B$9/100+C17*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6126,30 +7285,33 @@
         <v>83.5</v>
       </c>
       <c r="D18" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="E18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="F18" s="17" t="n">
         <v>92</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="G18" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="H18" s="17" t="n">
         <v>96</v>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="I18" s="17" t="n">
         <v>90</v>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="J18" s="17" t="n">
         <v>88</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="K18" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="K18" s="17" t="n">
+      <c r="L18" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="L18" s="12">
+      <c r="M18" s="12">
         <f>IFERROR(B18*INPUTS!$B$9/100+C18*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6167,30 +7329,33 @@
         <v>16.5</v>
       </c>
       <c r="D19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="F19" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="G19" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="H19" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="I19" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="J19" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="K19" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="L19" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="L19" s="12">
+      <c r="M19" s="12">
         <f>IFERROR(B19*INPUTS!$B$9/100+C19*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6208,30 +7373,33 @@
         <v>30.7</v>
       </c>
       <c r="D20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="F20" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="G20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="H20" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="H20" s="17" t="n">
+      <c r="I20" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="I20" s="17" t="n">
+      <c r="J20" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="K20" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="L20" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="L20" s="12">
+      <c r="M20" s="12">
         <f>IFERROR(B20*INPUTS!$B$9/100+C20*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6249,30 +7417,33 @@
         <v>22</v>
       </c>
       <c r="D21" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="F21" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="G21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="H21" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H21" s="17" t="n">
+      <c r="I21" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="I21" s="17" t="n">
+      <c r="J21" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="K21" s="17" t="n">
         <v>38</v>
       </c>
-      <c r="K21" s="17" t="n">
+      <c r="L21" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="12">
+      <c r="M21" s="12">
         <f>IFERROR(B21*INPUTS!$B$9/100+C21*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6290,30 +7461,33 @@
         <v>20</v>
       </c>
       <c r="D22" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="F22" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="G22" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="H22" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="H22" s="17" t="n">
+      <c r="I22" s="17" t="n">
         <v>65</v>
       </c>
-      <c r="I22" s="17" t="n">
+      <c r="J22" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="K22" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="K22" s="17" t="n">
+      <c r="L22" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="L22" s="12">
+      <c r="M22" s="12">
         <f>IFERROR(B22*INPUTS!$B$9/100+C22*INPUTS!$B$10/100,0)</f>
         <v/>
       </c>
@@ -6335,6 +7509,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -6389,6 +7564,10 @@
         <f>IFERROR(K7*K4/100,0)</f>
         <v/>
       </c>
+      <c r="L26" s="19">
+        <f>IFERROR(L7*L4/100,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -6436,6 +7615,10 @@
         <f>IFERROR(K8*K4/100,0)</f>
         <v/>
       </c>
+      <c r="L27" s="19">
+        <f>IFERROR(L8*L4/100,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -6483,6 +7666,10 @@
         <f>IFERROR(K9*K4/100,0)</f>
         <v/>
       </c>
+      <c r="L28" s="19">
+        <f>IFERROR(L9*L4/100,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -6530,6 +7717,10 @@
         <f>IFERROR(K10*K4/100,0)</f>
         <v/>
       </c>
+      <c r="L29" s="19">
+        <f>IFERROR(L10*L4/100,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -6575,6 +7766,10 @@
       </c>
       <c r="K30" s="19">
         <f>IFERROR(K11*K4/100,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="19">
+        <f>IFERROR(L11*L4/100,0)</f>
         <v/>
       </c>
     </row>
@@ -7065,7 +8260,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L6,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M6,0)</f>
         <v/>
       </c>
       <c r="C5" s="6" t="n">
@@ -7084,7 +8279,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L5,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M5,0)</f>
         <v/>
       </c>
       <c r="C6" s="6">
@@ -7104,7 +8299,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L4,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M4,0)</f>
         <v/>
       </c>
       <c r="C7" s="6">
@@ -7124,7 +8319,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L20,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M20,0)</f>
         <v/>
       </c>
       <c r="C8" s="6">
@@ -7144,7 +8339,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L21,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M21,0)</f>
         <v/>
       </c>
       <c r="C9" s="6">
@@ -7164,7 +8359,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L22,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M22,0)</f>
         <v/>
       </c>
       <c r="C10" s="6">
@@ -7184,7 +8379,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L7,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M7,0)</f>
         <v/>
       </c>
       <c r="C11" s="6">
@@ -7204,7 +8399,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L8,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M8,0)</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -7224,7 +8419,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>IFERROR(S0_Lab_Analysis!L9,0)</f>
+        <f>IFERROR(S0_Lab_Analysis!M9,0)</f>
         <v/>
       </c>
       <c r="C13" s="6">

--- a/CFI_Master_Excel.xlsx
+++ b/CFI_Master_Excel.xlsx
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -349,6 +349,13 @@
     </xf>
     <xf numFmtId="167" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -4542,13 +4549,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5861,285 +5870,1562 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TOTAL CAPEX SUMMARY</t>
+          <t>MOBILE EQUIPMENT &amp; VEHICLES</t>
         </is>
       </c>
       <c r="B99" s="3" t="n"/>
       <c r="C99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="38" t="inlineStr">
-        <is>
-          <t>TOTAL CAPEX</t>
-        </is>
-      </c>
-      <c r="B100" s="51">
-        <f>IFERROR(SUM(B5:B99),0)</f>
-        <v/>
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>Wheel Loader — Komatsu WA100 or equiv (1.0m3 bucket, EFB/OPDC handling)</t>
+        </is>
+      </c>
+      <c r="B101" s="46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="3" t="n"/>
-      <c r="D102" s="3" t="n"/>
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>Wheel Loader — Komatsu WA70 or equiv (0.5m3 bucket, PKSA/compost)</t>
+        </is>
+      </c>
+      <c r="B102" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>Cost Item</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>Monthly Cost (USD)</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>Skid-Steer Loader / Bobcat — S650 or equiv (BSF frass, substrate)</t>
+        </is>
+      </c>
+      <c r="B103" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Chemical Treatment</t>
-        </is>
-      </c>
-      <c r="B104" s="22">
-        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 2</t>
+          <t>Skid-Steer Loader / Bobcat — S450 or equiv (greenhouse internal)</t>
+        </is>
+      </c>
+      <c r="B104" s="46" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Biological Treatment</t>
-        </is>
-      </c>
-      <c r="B105" s="22">
-        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 3</t>
+          <t>Mini Excavator — 3.5t (site maintenance, drainage, pit cleaning)</t>
+        </is>
+      </c>
+      <c r="B105" s="46" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>BSF Neonates</t>
-        </is>
-      </c>
-      <c r="B106" s="22">
-        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
-        <v/>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 4</t>
+          <t>Dump Truck — 10t (EFB transport mill to S1, internal)</t>
+        </is>
+      </c>
+      <c r="B106" s="46" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Processing (S5B)</t>
-        </is>
-      </c>
-      <c r="B107" s="22">
-        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
-        <v/>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 5B</t>
+          <t>Dump Truck — 10t (OPDC/POS transport mill to S1)</t>
+        </is>
+      </c>
+      <c r="B107" s="46" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>Energy / Utilities</t>
-        </is>
-      </c>
-      <c r="B108" s="22">
-        <f>IFERROR(S1_Preprocessing!B30,0)</f>
-        <v/>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 1</t>
+          <t>Flatbed Truck — 8t (finished product transport, frass/meal)</t>
+        </is>
+      </c>
+      <c r="B108" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Labour (estimated)</t>
+          <t>Tanker Truck — 5,000L (water, POME, liquid transfer)</t>
         </is>
       </c>
       <c r="B109" s="46" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>10 workers @ $800/month</t>
+        <v>48000</v>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Maintenance (2% CAPEX/month)</t>
-        </is>
-      </c>
-      <c r="B110" s="22">
-        <f>IFERROR(B100*0.02/12,0)</f>
-        <v/>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Industry standard</t>
+          <t>Pickup Truck — 4x4 (site management, 2 units)</t>
+        </is>
+      </c>
+      <c r="B110" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Quality Control / Lab</t>
+          <t>Forklift — 3t diesel (warehouse, bagged product, 2 units)</t>
         </is>
       </c>
       <c r="B111" s="46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Monthly QC testing</t>
+        <v>50000</v>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
+          <t>Forklift — 1.5t electric (greenhouse internal, 2 units)</t>
+        </is>
+      </c>
+      <c r="B112" s="46" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>Tipping Trailer — 8t (substrate/frass haulage, 2 units)</t>
+        </is>
+      </c>
+      <c r="B113" s="46" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Pallet Jacks — manual (4 units, warehouse)</t>
+        </is>
+      </c>
+      <c r="B114" s="46" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>Grab Bucket Attachment — for wheel loader (EFB)</t>
+        </is>
+      </c>
+      <c r="B115" s="46" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>Sweeper Attachment — for bobcat (greenhouse cleaning)</t>
+        </is>
+      </c>
+      <c r="B116" s="46" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Mobile Equipment Subtotal</t>
+        </is>
+      </c>
+      <c r="B117" s="22">
+        <f>SUM(B101:B116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>STAFFING — FULL HEADCOUNT &amp; LABOUR COST</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n"/>
+      <c r="C119" s="3" t="n"/>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Salary (USD/month)</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Cost (USD)</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>S1 — EFB Line Operator (shredder + hammer mill)</t>
+        </is>
+      </c>
+      <c r="B121" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D121" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E121" s="22">
+        <f>B121*C121</f>
+        <v/>
+      </c>
+      <c r="F121" s="54" t="inlineStr">
+        <is>
+          <t>1 per shift, monitors feed + oversize return</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>S1 — EFB Conveyor / Screen Operator</t>
+        </is>
+      </c>
+      <c r="B122" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D122" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E122" s="22">
+        <f>B122*C122</f>
+        <v/>
+      </c>
+      <c r="F122" s="54" t="inlineStr">
+        <is>
+          <t>Belt + vibrating screen monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>S1 — EFB Screw Press Operator</t>
+        </is>
+      </c>
+      <c r="B123" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D123" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E123" s="22">
+        <f>B123*C123</f>
+        <v/>
+      </c>
+      <c r="F123" s="54" t="inlineStr">
+        <is>
+          <t>MC control, filtrate routing</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>S1 — OPDC Line Operator (shredder + hammer mill)</t>
+        </is>
+      </c>
+      <c r="B124" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D124" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E124" s="22">
+        <f>B124*C124</f>
+        <v/>
+      </c>
+      <c r="F124" s="54" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>S1 — OPDC Conveyor / Press Operator</t>
+        </is>
+      </c>
+      <c r="B125" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C125" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D125" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E125" s="22">
+        <f>B125*C125</f>
+        <v/>
+      </c>
+      <c r="F125" s="54" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>S1 — POS Decanter Operator</t>
+        </is>
+      </c>
+      <c r="B126" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="46" t="n">
+        <v>550</v>
+      </c>
+      <c r="D126" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E126" s="22">
+        <f>B126*C126</f>
+        <v/>
+      </c>
+      <c r="F126" s="54" t="inlineStr">
+        <is>
+          <t>Skilled: centrifuge operation + Fe gate sampling</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>S1 — Wheel Loader Operator (EFB/OPDC feed)</t>
+        </is>
+      </c>
+      <c r="B127" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D127" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E127" s="22">
+        <f>B127*C127</f>
+        <v/>
+      </c>
+      <c r="F127" s="54" t="inlineStr">
+        <is>
+          <t>Komatsu WA100</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>S1 — Dump Truck Driver (mill to S1)</t>
+        </is>
+      </c>
+      <c r="B128" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D128" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E128" s="22">
+        <f>B128*C128</f>
+        <v/>
+      </c>
+      <c r="F128" s="54" t="inlineStr">
+        <is>
+          <t>2x 10t dump trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>S2 — Chemical Dosing Operator</t>
+        </is>
+      </c>
+      <c r="B129" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D129" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E129" s="22">
+        <f>B129*C129</f>
+        <v/>
+      </c>
+      <c r="F129" s="54" t="inlineStr">
+        <is>
+          <t>PKSA/chemical mixing, pH monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>S2 — Neutralisation Bay Attendant</t>
+        </is>
+      </c>
+      <c r="B130" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C130" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D130" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E130" s="22">
+        <f>B130*C130</f>
+        <v/>
+      </c>
+      <c r="F130" s="54" t="inlineStr">
+        <is>
+          <t>Turnings at 8-12hr and 16-20hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>S3 — Biological Inoculation Technician</t>
+        </is>
+      </c>
+      <c r="B131" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="46" t="n">
+        <v>600</v>
+      </c>
+      <c r="D131" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E131" s="22">
+        <f>B131*C131</f>
+        <v/>
+      </c>
+      <c r="F131" s="54" t="inlineStr">
+        <is>
+          <t>Consortium preparation, spray application</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>S3 — Composting / Windrow Operator</t>
+        </is>
+      </c>
+      <c r="B132" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D132" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E132" s="22">
+        <f>B132*C132</f>
+        <v/>
+      </c>
+      <c r="F132" s="54" t="inlineStr">
+        <is>
+          <t>Windrow turner + aeration monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>S3 — Bobcat Operator (substrate handling)</t>
+        </is>
+      </c>
+      <c r="B133" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D133" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E133" s="22">
+        <f>B133*C133</f>
+        <v/>
+      </c>
+      <c r="F133" s="54" t="inlineStr">
+        <is>
+          <t>S650 skid-steer</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Greenhouse Supervisor</t>
+        </is>
+      </c>
+      <c r="B134" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="46" t="n">
+        <v>900</v>
+      </c>
+      <c r="D134" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E134" s="22">
+        <f>B134*C134</f>
+        <v/>
+      </c>
+      <c r="F134" s="54" t="inlineStr">
+        <is>
+          <t>Overall BSF rearing management</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>S4 — BSF Tray Attendant (feeding + monitoring)</t>
+        </is>
+      </c>
+      <c r="B135" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="C135" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D135" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E135" s="22">
+        <f>B135*C135</f>
+        <v/>
+      </c>
+      <c r="F135" s="54" t="inlineStr">
+        <is>
+          <t>4 per shift, 5000m2 per attendant</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>S4 — BSF Neonate Nursery Technician</t>
+        </is>
+      </c>
+      <c r="B136" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C136" s="46" t="n">
+        <v>550</v>
+      </c>
+      <c r="D136" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E136" s="22">
+        <f>B136*C136</f>
+        <v/>
+      </c>
+      <c r="F136" s="54" t="inlineStr">
+        <is>
+          <t>Colony management, egg collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Greenhouse Climate / IoT Technician</t>
+        </is>
+      </c>
+      <c r="B137" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="46" t="n">
+        <v>700</v>
+      </c>
+      <c r="D137" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E137" s="22">
+        <f>B137*C137</f>
+        <v/>
+      </c>
+      <c r="F137" s="54" t="inlineStr">
+        <is>
+          <t>SCADA/PLC, sensor maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Bobcat Operator (greenhouse internal)</t>
+        </is>
+      </c>
+      <c r="B138" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C138" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D138" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E138" s="22">
+        <f>B138*C138</f>
+        <v/>
+      </c>
+      <c r="F138" s="54" t="inlineStr">
+        <is>
+          <t>S450, substrate + frass movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Forklift Operator (greenhouse)</t>
+        </is>
+      </c>
+      <c r="B139" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D139" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E139" s="22">
+        <f>B139*C139</f>
+        <v/>
+      </c>
+      <c r="F139" s="54" t="inlineStr">
+        <is>
+          <t>1.5t electric forklifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>S5A — Frass Screening / Bagging Operator</t>
+        </is>
+      </c>
+      <c r="B140" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C140" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D140" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E140" s="22">
+        <f>B140*C140</f>
+        <v/>
+      </c>
+      <c r="F140" s="54" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>S5B — Larvae Separation Operator</t>
+        </is>
+      </c>
+      <c r="B141" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C141" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D141" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E141" s="22">
+        <f>B141*C141</f>
+        <v/>
+      </c>
+      <c r="F141" s="54" t="inlineStr">
+        <is>
+          <t>Vibrating separator + thermal</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>S5B — Oil Press / Dryer Operator</t>
+        </is>
+      </c>
+      <c r="B142" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C142" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D142" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E142" s="22">
+        <f>B142*C142</f>
+        <v/>
+      </c>
+      <c r="F142" s="54" t="inlineStr">
+        <is>
+          <t>Screw press + belt dryer</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>Warehouse — Forklift Operator</t>
+        </is>
+      </c>
+      <c r="B143" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C143" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D143" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E143" s="22">
+        <f>B143*C143</f>
+        <v/>
+      </c>
+      <c r="F143" s="54" t="inlineStr">
+        <is>
+          <t>3t diesel forklift</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>Warehouse — Storeman / Inventory</t>
+        </is>
+      </c>
+      <c r="B144" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D144" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E144" s="22">
+        <f>B144*C144</f>
+        <v/>
+      </c>
+      <c r="F144" s="54" t="inlineStr">
+        <is>
+          <t>Stock control, dispatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>Logistics — Flatbed Truck Driver</t>
+        </is>
+      </c>
+      <c r="B145" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D145" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E145" s="22">
+        <f>B145*C145</f>
+        <v/>
+      </c>
+      <c r="F145" s="54" t="inlineStr">
+        <is>
+          <t>Product delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>Logistics — Tanker Truck Driver</t>
+        </is>
+      </c>
+      <c r="B146" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D146" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E146" s="22">
+        <f>B146*C146</f>
+        <v/>
+      </c>
+      <c r="F146" s="54" t="inlineStr">
+        <is>
+          <t>Water/POME</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="B147" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D147" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E147" s="22">
+        <f>B147*C147</f>
+        <v/>
+      </c>
+      <c r="F147" s="54" t="inlineStr">
+        <is>
+          <t>Overall plant management</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>Production Supervisor (S1-S3)</t>
+        </is>
+      </c>
+      <c r="B148" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D148" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E148" s="22">
+        <f>B148*C148</f>
+        <v/>
+      </c>
+      <c r="F148" s="54" t="inlineStr">
+        <is>
+          <t>Preprocessing + treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>Quality Control / Lab Technician</t>
+        </is>
+      </c>
+      <c r="B149" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" s="46" t="n">
+        <v>650</v>
+      </c>
+      <c r="D149" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E149" s="22">
+        <f>B149*C149</f>
+        <v/>
+      </c>
+      <c r="F149" s="54" t="inlineStr">
+        <is>
+          <t>pH, MC, ICP-OES, sampling</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance Technician (mechanical)</t>
+        </is>
+      </c>
+      <c r="B150" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C150" s="46" t="n">
+        <v>600</v>
+      </c>
+      <c r="D150" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E150" s="22">
+        <f>B150*C150</f>
+        <v/>
+      </c>
+      <c r="F150" s="54" t="inlineStr">
+        <is>
+          <t>All mechanical equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance Technician (electrical/IoT)</t>
+        </is>
+      </c>
+      <c r="B151" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="46" t="n">
+        <v>650</v>
+      </c>
+      <c r="D151" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E151" s="22">
+        <f>B151*C151</f>
+        <v/>
+      </c>
+      <c r="F151" s="54" t="inlineStr">
+        <is>
+          <t>Electrical, sensors, PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>HSE Officer</t>
+        </is>
+      </c>
+      <c r="B152" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="46" t="n">
+        <v>700</v>
+      </c>
+      <c r="D152" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E152" s="22">
+        <f>B152*C152</f>
+        <v/>
+      </c>
+      <c r="F152" s="54" t="inlineStr">
+        <is>
+          <t>Safety, PPE, NaOH handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>Admin / Finance</t>
+        </is>
+      </c>
+      <c r="B153" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D153" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E153" s="22">
+        <f>B153*C153</f>
+        <v/>
+      </c>
+      <c r="F153" s="54" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>Security (gate + night)</t>
+        </is>
+      </c>
+      <c r="B154" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" s="46" t="n">
+        <v>350</v>
+      </c>
+      <c r="D154" s="53" t="inlineStr">
+        <is>
+          <t>3-shift</t>
+        </is>
+      </c>
+      <c r="E154" s="22">
+        <f>B154*C154</f>
+        <v/>
+      </c>
+      <c r="F154" s="54" t="inlineStr">
+        <is>
+          <t>24/7 coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>Cleaner / General Labour</t>
+        </is>
+      </c>
+      <c r="B155" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" s="46" t="n">
+        <v>350</v>
+      </c>
+      <c r="D155" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E155" s="22">
+        <f>B155*C155</f>
+        <v/>
+      </c>
+      <c r="F155" s="54" t="inlineStr">
+        <is>
+          <t>Site-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL STAFFING</t>
+        </is>
+      </c>
+      <c r="B156" s="55">
+        <f>SUM(B121:B155)</f>
+        <v/>
+      </c>
+      <c r="E156" s="51">
+        <f>SUM(E121:E155)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>ANNUAL LABOUR COST (x12 months)</t>
+        </is>
+      </c>
+      <c r="E157" s="22">
+        <f>E156*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX SUMMARY</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n"/>
+      <c r="C159" s="3" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX</t>
+        </is>
+      </c>
+      <c r="B160" s="51">
+        <f>IFERROR(SUM(B5:B159),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n"/>
+      <c r="C162" s="3" t="n"/>
+      <c r="D162" s="3" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>Cost Item</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>Chemical Treatment</t>
+        </is>
+      </c>
+      <c r="B164" s="22">
+        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
+        <v/>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="inlineStr">
+        <is>
+          <t>Biological Treatment</t>
+        </is>
+      </c>
+      <c r="B165" s="22">
+        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
+        <v/>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>BSF Neonates</t>
+        </is>
+      </c>
+      <c r="B166" s="22">
+        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
+        <v/>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>Processing (S5B)</t>
+        </is>
+      </c>
+      <c r="B167" s="22">
+        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
+        <v/>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="inlineStr">
+        <is>
+          <t>Energy / Utilities</t>
+        </is>
+      </c>
+      <c r="B168" s="22">
+        <f>IFERROR(S1_Preprocessing!B30,0)</f>
+        <v/>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="inlineStr">
+        <is>
+          <t>Labour (full staffing)</t>
+        </is>
+      </c>
+      <c r="B169" s="22">
+        <f>E156</f>
+        <v/>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>67 staff — see staffing section row 156</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance (2% CAPEX/month)</t>
+        </is>
+      </c>
+      <c r="B170" s="22">
+        <f>IFERROR(B160*0.02/12,0)</f>
+        <v/>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Industry standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>Quality Control / Lab</t>
+        </is>
+      </c>
+      <c r="B171" s="46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Monthly QC testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="inlineStr">
+        <is>
           <t>Transport / Logistics</t>
         </is>
       </c>
-      <c r="B112" s="46" t="n">
+      <c r="B172" s="46" t="n">
         <v>3000</v>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>Product distribution</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="38" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="38" t="inlineStr">
         <is>
           <t>TOTAL MONTHLY OPEX</t>
         </is>
       </c>
-      <c r="B113" s="52">
-        <f>IFERROR(SUM(B104:B112),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="B173" s="52">
+        <f>IFERROR(SUM(B164:B172),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>PAYBACK &amp; NPV ANALYSIS</t>
         </is>
       </c>
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="3" t="n"/>
-      <c r="D115" s="3" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="B175" s="3" t="n"/>
+      <c r="C175" s="3" t="n"/>
+      <c r="D175" s="3" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
         <is>
           <t>Total CAPEX</t>
         </is>
       </c>
-      <c r="B116" s="22">
-        <f>B100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="B176" s="22">
+        <f>B160</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>Monthly Gross Profit</t>
         </is>
       </c>
-      <c r="B117" s="22">
-        <f>IFERROR(Summary_Dashboard!B24-B113,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="38" t="inlineStr">
+      <c r="B177" s="22">
+        <f>IFERROR(Summary_Dashboard!B24-B173,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="38" t="inlineStr">
         <is>
           <t>Payback Period (months)</t>
         </is>
       </c>
-      <c r="B118" s="42">
-        <f>IFERROR(B116/B117,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="B178" s="42">
+        <f>IFERROR(B176/B177,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>Payback Period (years)</t>
         </is>
       </c>
-      <c r="B119" s="13">
-        <f>IFERROR(B118/12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="B179" s="13">
+        <f>IFERROR(B178/12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
         <is>
           <t>IRR Discount Rate (user-adjustable)</t>
         </is>
       </c>
-      <c r="B121" s="53" t="n">
+      <c r="B181" s="56" t="n">
         <v>0.12</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>Annual Net Cash Flow</t>
         </is>
       </c>
-      <c r="B122" s="22">
-        <f>IFERROR(B117*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="7" t="inlineStr">
+      <c r="B182" s="22">
+        <f>IFERROR(B177*12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
         <is>
           <t>5-Year NPV (simple estimate)</t>
         </is>
       </c>
-      <c r="B123" s="30">
-        <f>IFERROR(B122/(1+B121)^1+B122/(1+B121)^2+B122/(1+B121)^3+B122/(1+B121)^4+B122/(1+B121)^5-B116,0)</f>
+      <c r="B183" s="30">
+        <f>IFERROR(B182/(1+B181)^1+B182/(1+B181)^2+B182/(1+B181)^3+B182/(1+B181)^4+B182/(1+B181)^5-B176,0)</f>
         <v/>
       </c>
     </row>

--- a/CFI_Master_Excel.xlsx
+++ b/CFI_Master_Excel.xlsx
@@ -140,7 +140,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -175,6 +175,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FF4444"/>
         <bgColor rgb="00FF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -248,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -350,6 +356,7 @@
     <xf numFmtId="167" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4549,7 +4556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4570,7 +4577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>S1 — EFB PROCESSING LINE (20 t/h, 153kW nameplate)</t>
+          <t>S1 — EFB MECHANICAL PRE-PROCESSING (21 items, $336,250 — CAPEX v4.1)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -4596,11 +4603,11 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>RCV-EFB-01 — EFB Receiving Hopper (50m3, hydraulic gate)</t>
+          <t>TR-EFB-101 — Truck Receiving Bay (concrete ramp 6m×4m, 1.2m high)</t>
         </is>
       </c>
       <c r="B5" s="46" t="n">
-        <v>28000</v>
+        <v>8000</v>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
@@ -4611,11 +4618,11 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>CVB-EFB-01 — Drag Chain Conveyor (12m x 600mm, VFD, 7.5kW)</t>
+          <t>RH-EFB-101 — Receiving Hopper 20m3 (304SS liner, 60deg walls, ultrasonic sensor)</t>
         </is>
       </c>
       <c r="B6" s="46" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
@@ -4626,11 +4633,11 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>ESD-01 — Primary Twin-Shaft Shredder (2x37kW = 74kW, 15-25 RPM)</t>
+          <t>AF-01 — Apron Feeder (3.5m×1.2m, AR400 pans, VFD 2-8 m/min, 7.5kW)</t>
         </is>
       </c>
       <c r="B7" s="46" t="n">
-        <v>95000</v>
+        <v>12000</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
@@ -4641,11 +4648,11 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>CVB-EFB-02 — Incline Belt Conveyor (8m x 600mm, 30deg, 5.5kW)</t>
+          <t>BC-01 — Belt Conveyor hopper-trommel (500mm belt, 4.5kW)</t>
         </is>
       </c>
       <c r="B8" s="46" t="n">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
@@ -4656,11 +4663,11 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>BIN-EFB-01 — Buffer Bin (50m3, VFD screw feeder, 2.5hr cap)</t>
+          <t>TR-2060 — Trommel Screen (2m dia×6m, 20mm perf, 10-15 RPM, 7.5kW)</t>
         </is>
       </c>
       <c r="B9" s="46" t="n">
-        <v>22000</v>
+        <v>21500</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
@@ -4671,11 +4678,11 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>ELB-01 — Lump Breaker twin-roller (30-50mm gap, 11kW)</t>
+          <t>BC-02 — Belt Conveyor trommel-magnet (4.5kW)</t>
         </is>
       </c>
       <c r="B10" s="46" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
@@ -4686,11 +4693,11 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>EHM-01 — Hammer Mill (2mm screen, 37kW nameplate/24kW derated)</t>
+          <t>OBM-01 — Overband Magnet (self-cleaning belt, 250-400mm, 2.2kW)</t>
         </is>
       </c>
       <c r="B11" s="46" t="n">
-        <v>65000</v>
+        <v>6750</v>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
@@ -4701,11 +4708,11 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>ESC-01 — Vibrating Screen linear (2mm mesh, 2x1.5kW)</t>
+          <t>BC-04 — Belt Conveyor magnet-metal detector (4.5kW)</t>
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>18000</v>
+        <v>7500</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
@@ -4716,11 +4723,11 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>EPR-01 — Screw Press twin-screw (62.5%-&gt;45-50% MC, 15kW)</t>
+          <t>MD-01 — Metal Detector (tunnel 1000×200mm, auto-reject gate, 0.5kW)</t>
         </is>
       </c>
       <c r="B13" s="46" t="n">
-        <v>55000</v>
+        <v>8500</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
@@ -4731,11 +4738,11 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>BIN-EFB-301 — S2 Buffer Bin (50m3, 2.5hr)</t>
+          <t>PR-01 — Screw Press CB-20T/C DUTY (37kW, 70pct-45-50pct MC, 13.8-9.8 t/hr)</t>
         </is>
       </c>
       <c r="B14" s="46" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
@@ -4746,11 +4753,11 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>EDC-01 — Baghouse Dust Collection</t>
+          <t>PR-01B — Screw Press CB-20T/C STANDBY (immutable backup, 37kW)</t>
         </is>
       </c>
       <c r="B15" s="46" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
@@ -4759,200 +4766,200 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>S1 EFB Subtotal</t>
-        </is>
-      </c>
-      <c r="B16" s="22">
-        <f>SUM(B5:B15)</f>
-        <v/>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>BC-05 — Belt Conveyor press-shredder (4.5kW)</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>S1-EFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>SD-01 — Primary Shredder KH-777 (dual shaft, AR400, 100-200-30-50mm, 90kW)</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>S1-EFB</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>S1 — OPDC PROCESSING LINE (5 t/h, 96.2kW nameplate)</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>BC-06 — Belt Conveyor shredder-hammer mill (4.5kW)</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>S1-EFB</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Equipment / Item</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Estimated Cost (USD)</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>HM-01 — Hammer Mill YTH-7.100 (1800 RPM, D90&lt;=2mm, 55kW, spring isolation)</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n">
+        <v>18500</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>RCV-OPDC-01 — OPDC Receiving Hopper (20m3, hydraulic gate)</t>
+          <t>BC-07 — Belt Conveyor hammer mill-vibrating screen (4.5kW)</t>
         </is>
       </c>
       <c r="B20" s="46" t="n">
-        <v>18000</v>
+        <v>7500</v>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>S1-OPDC</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>CVB-OPDC-01 — Drag Chain Conveyor (10m x 500mm, VFD, 5.5kW)</t>
+          <t>VS-01 — Vibrating Screen 2mm (D90&lt;=2mm CLASS A gate, 1.5kW)</t>
         </is>
       </c>
       <c r="B21" s="46" t="n">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>S1-OPDC</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>OSD-01 — Primary Twin-Shaft Shredder (2x22kW = 44kW, 15-25 RPM)</t>
+          <t>BC-08 — Belt Conveyor oversize recycle-HM-01 (2.2kW)</t>
         </is>
       </c>
       <c r="B22" s="46" t="n">
-        <v>72000</v>
+        <v>5500</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>S1-OPDC</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>CVB-OPDC-02 — Incline Belt Conveyor (7m x 500mm, 30deg, 4kW)</t>
+          <t>BC-09 — Belt Conveyor undersize-buffer bin (4.5kW)</t>
         </is>
       </c>
       <c r="B23" s="46" t="n">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>S1-OPDC</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>BIN-OPDC-01 — Buffer Bin (20m3, VFD screw feeder, 4hr cap)</t>
+          <t>BIN-EFB-201 — Buffer Bin 50m3 (live bottom, ~24hr dwell before S2)</t>
         </is>
       </c>
       <c r="B24" s="46" t="n">
-        <v>16000</v>
+        <v>25000</v>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>S1-OPDC</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>OLB-01 — Lump Breaker twin-roller (25-40mm gap, 7.5kW)</t>
+          <t>EDC-01 — Dust Collector Baghouse (15,000 CFM, 200mm ducts, 18kW)</t>
         </is>
       </c>
       <c r="B25" s="46" t="n">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>S1-OPDC</t>
+          <t>S1-EFB</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>OHM-01 — Hammer Mill (2mm screen, 22kW nameplate/14kW derated)</t>
-        </is>
-      </c>
-      <c r="B26" s="46" t="n">
-        <v>48000</v>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>S1-OPDC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>OSC-01 — Vibrating Screen linear (2mm mesh, 2x1.1kW)</t>
-        </is>
-      </c>
-      <c r="B27" s="46" t="n">
-        <v>14000</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>S1-OPDC</t>
-        </is>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>S1 EFB Subtotal</t>
+        </is>
+      </c>
+      <c r="B26" s="22">
+        <f>SUM(B5:B25)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>OPR-01 — Screw Press twin-screw (70-75%-&gt;60-62% MC, 11kW)</t>
-        </is>
-      </c>
-      <c r="B28" s="46" t="n">
-        <v>42000</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>S1-OPDC</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>S1 — OPDC DEWATERING + BUFFER (11 items, $204,000 — CAPEX v4.1)</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>BIN-OPDC-301 — S2 Buffer Bin (15m3 concrete/carbon steel)</t>
-        </is>
-      </c>
-      <c r="B29" s="46" t="n">
-        <v>14000</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>S1-OPDC</t>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>ODC-01 — Baghouse Dust Collection</t>
+          <t>TR-OPDC-101 — Receiving Bay (concrete ramp, epoxy-coated hopper 15m3)</t>
         </is>
       </c>
       <c r="B30" s="46" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
@@ -4961,2471 +4968,3511 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>S1 OPDC Subtotal</t>
-        </is>
-      </c>
-      <c r="B31" s="22">
-        <f>SUM(B20:B30)</f>
-        <v/>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>RH-OPDC-101 — Receiving Hopper 15m3 (3.5m×2.5m×2m, 150mm drain valve)</t>
+        </is>
+      </c>
+      <c r="B31" s="46" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>SF-01 — Screw Feeder DC (3m×300mm, 304SS, VFD 10-50 RPM, 5.5kW)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>S1 — POS PROCESSING LINE (1.25 t/h, 20.2kW)</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>BC-10 — Belt Conveyor OPDC hopper-belt press (oil-resistant, 2.2kW)</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Equipment / Item</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Estimated Cost (USD)</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>PR-301 — Belt Filter Press Biorem MDS (70-75pct-60-62pct MC, 15-30kW) NEVER&lt;40pct</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PIT-POS-01 — POS Reception Pit (15m3, RC concrete, epoxy-coated)</t>
+          <t>BC-11 — Belt Conveyor belt press cake-loosener (2.2kW)</t>
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>S1-POS</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>T-SLD-101 — Sludge Holding Tank (5-8m3, SS304, sealed dome, 3.7kW agitator)</t>
+          <t>SD-301 — Finger-Screw Loosener/Lump Breaker (LOW SPEED ONLY, 37kW)</t>
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>S1-POS</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PMP-POS-01 — Sludge Transfer Pump (progressive cavity, SS316L, 5.5kW, VFD)</t>
+          <t>BC-SPRAY — Chemical Spray Conveyor 304SS (3-5m belt, PKSA coating, 2-4kW)</t>
         </is>
       </c>
       <c r="B37" s="46" t="n">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>S1-POS</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>DCN-POS-01 — Decanter Centrifuge 3-phase (1.5t/h, Alfa Laval, 11kW)</t>
+          <t>BUN-301 — Covered Buffer Bunker ~85t FW (concrete push-wall, 24-48hr pH dwell)</t>
         </is>
       </c>
       <c r="B38" s="46" t="n">
-        <v>120000</v>
+        <v>30000</v>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>S1-POS</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>BUF-POS-01 — S2 Buffer Bin (5m3, carbon steel + epoxy)</t>
+          <t>SIL-301 — EFB+OPDC Blending Silo (&gt;=45deg conical base, sweep auger, 4-7.5kW)</t>
         </is>
       </c>
       <c r="B39" s="46" t="n">
-        <v>12000</v>
+        <v>55000</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>S1-POS</t>
+          <t>S1-OPDC</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>S1 POS Subtotal</t>
-        </is>
-      </c>
-      <c r="B40" s="22">
-        <f>SUM(B35:B39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>S2 CHEMICAL + S3 BIOLOGICAL — HANDOFF EQUIPMENT</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>BIN-OPDC-301 — Buffer Bin 20m3 (steel bin S1 discharge holding)</t>
+        </is>
+      </c>
+      <c r="B40" s="46" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>S1-OPDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>S1 OPDC Subtotal</t>
+        </is>
+      </c>
+      <c r="B41" s="22">
+        <f>SUM(B30:B40)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>S1 — POS/SLUDGE LINE (6 items, $154,000 — DEC=RFQ — CAPEX v4.1)</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Equipment / Item</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Estimated Cost (USD)</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>S2 Chemical Mixing Tank (covered, 20m3, paddle mixer, 15kW)</t>
-        </is>
-      </c>
-      <c r="B44" s="46" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>S2 pH Monitoring Station (inline pH probe + datalogger)</t>
+          <t>DEC-SLD-101 — 3-Phase Decanter Centrifuge (3 m3/hr, 304SS bowl, 15-30kW) RFQ ONLY</t>
         </is>
       </c>
       <c r="B45" s="46" t="n">
-        <v>5000</v>
+        <v>115000</v>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>S2-S3</t>
+          <t>S1-POS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>S2 Neutralisation Bays (3x concrete bays, 50m3 each)</t>
+          <t>P-SLD-101A — Sludge Feed Pump DUTY (progressive cavity 3-4 m3/hr, 7.5kW, 304SS)</t>
         </is>
       </c>
       <c r="B46" s="46" t="n">
-        <v>45000</v>
+        <v>8000</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>S2-S3</t>
+          <t>S1-POS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>S2-S3 Transfer Conveyor (covered belt, 15m, 5.5kW)</t>
+          <t>P-SLD-101B — Sludge Feed Pump STANDBY (auto-switchover, 7.5kW)</t>
         </is>
       </c>
       <c r="B47" s="46" t="n">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>S2-S3</t>
+          <t>S1-POS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>S3 Biological Inoculation System (spray boom + tank)</t>
+          <t>T-SLD-101 — Sludge Buffer Tank 6-8m3 (304SS, 2.2kW agitator, sealed, H2S vent)</t>
         </is>
       </c>
       <c r="B48" s="46" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>S2-S3</t>
+          <t>S1-POS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>S3 Composting Bays (covered, 5x 100m2 windrow bays)</t>
+          <t>T-OIL-101 — Recovered Sludge Oil Tank 10m3 (carbon steel, bund, level gauge)</t>
         </is>
       </c>
       <c r="B49" s="46" t="n">
-        <v>60000</v>
+        <v>8000</v>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>S2-S3</t>
+          <t>S1-POS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>S3 Aeration System (forced air + temperature probes)</t>
+          <t>P-OIL-101 — Recovered Oil Transfer Pump (centrifugal/gear 5 m3/hr, 1.5kW)</t>
         </is>
       </c>
       <c r="B50" s="46" t="n">
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>S2-S3</t>
+          <t>S1-POS</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>S3 Turning Machine (windrow turner, 22kW)</t>
-        </is>
-      </c>
-      <c r="B51" s="46" t="n">
-        <v>55000</v>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>S2-S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>S2-S3 Subtotal</t>
-        </is>
-      </c>
-      <c r="B52" s="22">
-        <f>SUM(B44:B51)</f>
-        <v/>
-      </c>
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>S1 POS Subtotal</t>
+        </is>
+      </c>
+      <c r="B51" s="22">
+        <f>SUM(B45:B50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>S2 — OPDC PKSA CHEMICAL TREATMENT (13 items, $162,000 — CAPEX v4.1)</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>BSF GREENHOUSE + IoT + AUTOMATION (20,000 m2)</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Equipment / Item</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Estimated Cost (USD)</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>M-OPDC-PKSA-01 — Paddle Mixer #1 (2t wet/batch, 75min, alkaline+oil resistant, 11kW)</t>
+        </is>
+      </c>
+      <c r="B55" s="46" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse Structure — Steel frame, poly-carbonate panels (20,000 m2)</t>
+          <t>M-OPDC-PKSA-02 — Paddle Mixer #2 (2t/batch, 11kW)</t>
         </is>
       </c>
       <c r="B56" s="46" t="n">
-        <v>1200000</v>
+        <v>18000</v>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse Foundation — Concrete slab + drainage (20,000 m2)</t>
+          <t>CV-OPDC-FEED-01 — Feed Screw Mixer 1 from BIN-OPDC-301 (2 t/hr, 2.2kW)</t>
         </is>
       </c>
       <c r="B57" s="46" t="n">
-        <v>400000</v>
+        <v>3500</v>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Internal Partition Walls — BSF zone separation (40 bays x 500m2)</t>
+          <t>CV-OPDC-FEED-02 — Feed Screw Mixer 2 (2 t/hr, 2.2kW)</t>
         </is>
       </c>
       <c r="B58" s="46" t="n">
-        <v>120000</v>
+        <v>3500</v>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Rearing Tray System — Stacked 3-tier racks (20,000 m2 effective)</t>
+          <t>T-PKSA-OPDC-01 — PKSA Slurry Tank 10m3 HDPE + agitator (1.5kW)</t>
         </is>
       </c>
       <c r="B59" s="46" t="n">
-        <v>350000</v>
+        <v>6000</v>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Blackout System — UV-blocking curtains + light baffles</t>
+          <t>P-PKSA-OPDC-01 — PKSA Slurry Pump centrifugal 5 m3/hr (1.5kW)</t>
         </is>
       </c>
       <c r="B60" s="46" t="n">
-        <v>80000</v>
+        <v>3000</v>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>HVAC System — Evaporative cooling + exhaust fans (20,000 m2)</t>
+          <t>SPR-OPDC-01 — PKSA Spray System (spray bars, 2 mixers)</t>
         </is>
       </c>
       <c r="B61" s="46" t="n">
-        <v>280000</v>
+        <v>3000</v>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Heating System — Hot water pipes from mill waste heat</t>
+          <t>CV-OPDC-COL-01 — Collection Screw under mixers (3 t/hr, 3kW)</t>
         </is>
       </c>
       <c r="B62" s="46" t="n">
-        <v>150000</v>
+        <v>8000</v>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Humidification System — Fogging nozzles + RH control</t>
+          <t>CV-OPDC-INCL-01 — Inclined Conveyor to bay level (3 t/hr, 4.5kW)</t>
         </is>
       </c>
       <c r="B63" s="46" t="n">
-        <v>65000</v>
+        <v>10000</v>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Air Circulation Fans — 120 units, ceiling mount</t>
+          <t>CV-OPDC-DIST-01 — Distribution Conveyor above Row A (3 t/hr, 4.5kW)</t>
         </is>
       </c>
       <c r="B64" s="46" t="n">
-        <v>48000</v>
+        <v>12000</v>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>IoT Temperature Sensors — 200 units (5 per bay, wireless)</t>
+          <t>C-OPDC-BAY-A — Neutralisation Bays Row A x6 (12m×12m×1.5m RC, 2pct slope)</t>
         </is>
       </c>
       <c r="B65" s="46" t="n">
-        <v>30000</v>
+        <v>48000</v>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>IoT Humidity Sensors — 200 units (5 per bay, wireless)</t>
+          <t>C-OPDC-BAY-B — pH Trim Bays Row B x3</t>
         </is>
       </c>
       <c r="B66" s="46" t="n">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>IoT CO2 Sensors — 40 units (1 per bay)</t>
+          <t>S-OPDC-SPRAY-A-01 — Row A Liquor Sprinkler</t>
         </is>
       </c>
       <c r="B67" s="46" t="n">
-        <v>16000</v>
+        <v>5000</v>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>S2-OPDC</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>IoT pH Sensors — substrate monitoring, 80 units</t>
-        </is>
-      </c>
-      <c r="B68" s="46" t="n">
-        <v>24000</v>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>IoT/Automation</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>IoT Weight Sensors — tray scales for yield tracking, 200 units</t>
-        </is>
-      </c>
-      <c r="B69" s="46" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>IoT/Automation</t>
-        </is>
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>S2 OPDC Chemical Subtotal</t>
+        </is>
+      </c>
+      <c r="B68" s="22">
+        <f>SUM(B55:B67)</f>
+        <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>IoT Ammonia Sensors — 40 units (1 per bay)</t>
-        </is>
-      </c>
-      <c r="B70" s="46" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>IoT/Automation</t>
-        </is>
-      </c>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>S2-S3 DISPATCH: STORAGE + FINAL BLEND + TRUCK LOADING (14 items, $308,000 — CAPEX v4.1)</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>Central IoT Gateway — LoRaWAN/WiFi hub + cloud dashboard</t>
-        </is>
-      </c>
-      <c r="B71" s="46" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>IoT/Automation</t>
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>IoT Software Platform — Dashboard, alerts, analytics (annual license)</t>
+          <t>CV-BAY-COL-01 — Substrate Collection Conveyor from EFB bays (15 t/hr, 7.5kW)</t>
         </is>
       </c>
       <c r="B72" s="46" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Automated Feed Distribution System — conveyor + metering</t>
+          <t>CV-BAY-COL-02 — Substrate Collection Conveyor from OPDC bays (5 t/hr, 4.5kW)</t>
         </is>
       </c>
       <c r="B73" s="46" t="n">
-        <v>180000</v>
+        <v>12000</v>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Automated Larvae Harvesting System — vibrating separator + conveyor</t>
+          <t>HT-BLEND-01 — Horizontal Substrate Holding Tank #1 100m3 (carbon steel, 4kW)</t>
         </is>
       </c>
       <c r="B74" s="46" t="n">
-        <v>220000</v>
+        <v>35000</v>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Automated Tray Washing Station</t>
+          <t>HT-BLEND-02 — Horizontal Substrate Holding Tank #2 50m3 OPDC buffer (3kW)</t>
         </is>
       </c>
       <c r="B75" s="46" t="n">
-        <v>45000</v>
+        <v>22000</v>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Automated Climate Control PLC — Siemens/Allen-Bradley</t>
+          <t>WB-EFB-01 — EFB Weigh Belt Feeder (VFD, ratio control 60:40, 15 t/hr, 2.2kW)</t>
         </is>
       </c>
       <c r="B76" s="46" t="n">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>SCADA System — Central control room, 4 screens</t>
+          <t>WB-OPDC-01 — OPDC Weigh Belt Feeder (VFD, ratio control, 5 t/hr, 2.2kW)</t>
         </is>
       </c>
       <c r="B77" s="46" t="n">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Water Supply System — treatment + distribution (20,000 m2)</t>
+          <t>S-LIME-BLEND-01 — Limestone Auto-Auger Dosing CaCO3 (1.5kW) DATA GAP dose rate</t>
         </is>
       </c>
       <c r="B78" s="46" t="n">
-        <v>85000</v>
+        <v>15000</v>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Electrical Distribution — panels, cabling, backup genset</t>
+          <t>B-BLEND-01 — Continuous Paddle Blender #1 (60:40 DM, pH 7-8.5, 55pct MC, 11kW)</t>
         </is>
       </c>
       <c r="B79" s="46" t="n">
-        <v>120000</v>
+        <v>45000</v>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Waste Water Treatment — effluent from rearing</t>
+          <t>B-BLEND-02 — Continuous Paddle Blender #2 N+1 redundancy (11kW)</t>
         </is>
       </c>
       <c r="B80" s="46" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Fire Suppression System</t>
+          <t>pH-SENS-01 — Inline pH Sensor #1 blender discharge (GO/NO-GO gate)</t>
         </is>
       </c>
       <c r="B81" s="46" t="n">
-        <v>45000</v>
+        <v>3500</v>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Site Clearing &amp; Grading (2.5 ha total footprint)</t>
+          <t>pH-SENS-02 — Inline pH Sensor #2 redundant</t>
         </is>
       </c>
       <c r="B82" s="46" t="n">
-        <v>80000</v>
+        <v>3500</v>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Site Works</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Access Roads — Internal + connection to mill (500m gravel)</t>
+          <t>HT-FINAL-01 — Final Substrate Storage Tank 200m3 (walking-floor, 5.5kW)</t>
         </is>
       </c>
       <c r="B83" s="46" t="n">
-        <v>60000</v>
+        <v>65000</v>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Site Works</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Perimeter Fencing + Security</t>
+          <t>CV-DISPATCH-01 — Substrate Dispatch Inclined Conveyor 15m (15 t/hr, 7.5kW)</t>
         </is>
       </c>
       <c r="B84" s="46" t="n">
-        <v>35000</v>
+        <v>20000</v>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Drainage System — Surface + subsurface</t>
+          <t>CHUTE-TRUCK-01 — Truck Loading Chute (4m wide, 1.0-1.5m free fall)</t>
         </is>
       </c>
       <c r="B85" s="46" t="n">
-        <v>55000</v>
+        <v>8000</v>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Site Works</t>
+          <t>S2-S3</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>Landscaping + Erosion Control</t>
-        </is>
-      </c>
-      <c r="B86" s="46" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>Site Works</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>Staff Facilities — Office, changing rooms, canteen</t>
-        </is>
-      </c>
-      <c r="B87" s="46" t="n">
-        <v>85000</v>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>Facilities</t>
-        </is>
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>S2-S3 Dispatch Subtotal</t>
+        </is>
+      </c>
+      <c r="B86" s="22">
+        <f>SUM(B72:B85)</f>
+        <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>Storage Warehouse — Finished product (500 m2)</t>
-        </is>
-      </c>
-      <c r="B88" s="46" t="n">
-        <v>120000</v>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>Facilities</t>
-        </is>
-      </c>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>SHARED ALL STAGES + S3 FINAL BLEND (3 items, $111,000 — CAPEX v4.1)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Greenhouse + IoT Subtotal</t>
-        </is>
-      </c>
-      <c r="B89" s="22">
-        <f>SUM(B56:B88)</f>
-        <v/>
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Limestone Storage &amp; Dosing — CaCO3 manual bag discharge, covered, scales</t>
+        </is>
+      </c>
+      <c r="B90" s="46" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>S5 EXTRACTION &amp; POST-PROCESSING</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n"/>
-      <c r="C91" s="3" t="n"/>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Lonking/Bobcat FEL 3-5t diesel — bay-to-bay material transfer (55kW, shared)</t>
+        </is>
+      </c>
+      <c r="B91" s="46" t="n">
+        <v>75000</v>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>S5A — Frass screening/bagging line</t>
+          <t>Final Blending Hopper/Mixer 10-15m3 — EFB+OPDC pre-BSF, S3 (11kW)</t>
         </is>
       </c>
       <c r="B92" s="46" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>S5/Lab</t>
+          <t>Shared</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>S5B — Larvae separation (vibrating + thermal)</t>
-        </is>
-      </c>
-      <c r="B93" s="46" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>S5/Lab</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>S5B — Oil press (screw type, 85% eff)</t>
-        </is>
-      </c>
-      <c r="B94" s="46" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>S5/Lab</t>
-        </is>
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Shared Equipment Subtotal</t>
+        </is>
+      </c>
+      <c r="B93" s="22">
+        <f>SUM(B90:B92)</f>
+        <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>S5B — Drying system (belt dryer)</t>
-        </is>
-      </c>
-      <c r="B95" s="46" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>S5/Lab</t>
-        </is>
-      </c>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>PROCESS BUILDING CAPEX — EPC PACKAGES A1-A8 ($2,020,192 — CAPEX v4.1)</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n"/>
+      <c r="C95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Laboratory — QC lab (ICP-OES capable)</t>
-        </is>
-      </c>
-      <c r="B96" s="46" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>S5/Lab</t>
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>S5 Subtotal</t>
-        </is>
-      </c>
-      <c r="B97" s="22">
-        <f>SUM(B92:B96)</f>
-        <v/>
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>A1 — Site Works (clearance 2.5ha, earthworks, roads, drainage perimeter)</t>
+        </is>
+      </c>
+      <c r="B97" s="46" t="n">
+        <v>159750</v>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>EPC Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>A2 — Civil &amp; Concrete (slabs, foundations, hoppers, neutr.bays, sludge pad)</t>
+        </is>
+      </c>
+      <c r="B98" s="46" t="n">
+        <v>197720</v>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>EPC Base</t>
+        </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>MOBILE EQUIPMENT &amp; VEHICLES</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n"/>
-      <c r="C99" s="3" t="n"/>
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>A3 — Structural Steel &amp; Cladding (S1 PEB 36×35m×10m + S2 shed + bay roof)</t>
+        </is>
+      </c>
+      <c r="B99" s="46" t="n">
+        <v>570126</v>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>EPC Base</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>Equipment / Item</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>Estimated Cost (USD)</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>A4 — Welfare Fit-out (offices, changing, showers, canteen 40-pax, 50 lockers)</t>
+        </is>
+      </c>
+      <c r="B100" s="46" t="n">
+        <v>107650</v>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>EPC Base</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Wheel Loader — Komatsu WA100 or equiv (1.0m3 bucket, EFB/OPDC handling)</t>
+          <t>A5 — MEP Power &amp; Lighting (MCCs S1+S2, LV switchboard, cabling 250kW)</t>
         </is>
       </c>
       <c r="B101" s="46" t="n">
-        <v>85000</v>
+        <v>180005</v>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>EPC Base</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Wheel Loader — Komatsu WA70 or equiv (0.5m3 bucket, PKSA/compost)</t>
+          <t>A6 — MEP HVAC &amp; Ventilation (AC offices, dust extraction, H2S biofilter)</t>
         </is>
       </c>
       <c r="B102" s="46" t="n">
-        <v>55000</v>
+        <v>47160</v>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>EPC Base</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Skid-Steer Loader / Bobcat — S650 or equiv (BSF frass, substrate)</t>
+          <t>A7 — MEP Plumbing &amp; Drainage (water, POME routing, sludge feed, 250m3/day)</t>
         </is>
       </c>
       <c r="B103" s="46" t="n">
-        <v>45000</v>
+        <v>77790</v>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>EPC Base</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Skid-Steer Loader / Bobcat — S450 or equiv (greenhouse internal)</t>
+          <t>A8 — Process Building Items (supports, dust ducting, fire ext, safety railings)</t>
         </is>
       </c>
       <c r="B104" s="46" t="n">
-        <v>38000</v>
+        <v>62710</v>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>EPC Base</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Mini Excavator — 3.5t (site maintenance, drainage, pit cleaning)</t>
+          <t>EPC Contingency 8%</t>
         </is>
       </c>
       <c r="B105" s="46" t="n">
-        <v>42000</v>
+        <v>112233</v>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>EPC Markup</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Dump Truck — 10t (EFB transport mill to S1, internal)</t>
+          <t>EPC Overheads &amp; Margin 12%</t>
         </is>
       </c>
       <c r="B106" s="46" t="n">
-        <v>65000</v>
+        <v>168349</v>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>EPC Markup</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Dump Truck — 10t (OPDC/POS transport mill to S1)</t>
+          <t>Developer/Process Markup 20%</t>
         </is>
       </c>
       <c r="B107" s="46" t="n">
-        <v>65000</v>
+        <v>336699</v>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>EPC Markup</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>Flatbed Truck — 8t (finished product transport, frass/meal)</t>
-        </is>
-      </c>
-      <c r="B108" s="46" t="n">
-        <v>55000</v>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>Tanker Truck — 5,000L (water, POME, liquid transfer)</t>
-        </is>
-      </c>
-      <c r="B109" s="46" t="n">
-        <v>48000</v>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>Process Building TOTAL</t>
+        </is>
+      </c>
+      <c r="B108" s="22">
+        <f>SUM(B97:B107)</f>
+        <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>Pickup Truck — 4x4 (site management, 2 units)</t>
-        </is>
-      </c>
-      <c r="B110" s="46" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>ELECTRICAL PANELS &amp; CONTROLS (10 items, $227,500 — CAPEX v4.1)</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n"/>
+      <c r="C110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>Forklift — 3t diesel (warehouse, bagged product, 2 units)</t>
-        </is>
-      </c>
-      <c r="B111" s="46" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>Mobile</t>
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Forklift — 1.5t electric (greenhouse internal, 2 units)</t>
+          <t>ELEC-01 — Main Transformer 500kVA 11kV/400V (200kW + 25pct margin)</t>
         </is>
       </c>
       <c r="B112" s="46" t="n">
-        <v>36000</v>
+        <v>35000</v>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Tipping Trailer — 8t (substrate/frass haulage, 2 units)</t>
+          <t>ELEC-02 — LV Main Switchboard 400V 1000A ACB</t>
         </is>
       </c>
       <c r="B113" s="46" t="n">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Pallet Jacks — manual (4 units, warehouse)</t>
+          <t>ELEC-03 — MCC Panel EFB Line (motor starters, VFDs, relays ~100kW)</t>
         </is>
       </c>
       <c r="B114" s="46" t="n">
-        <v>3200</v>
+        <v>32500</v>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Grab Bucket Attachment — for wheel loader (EFB)</t>
+          <t>ELEC-04 — MCC Panel OPDC Line (motor starters, VFDs ~50kW)</t>
         </is>
       </c>
       <c r="B115" s="46" t="n">
-        <v>8000</v>
+        <v>32500</v>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Sweeper Attachment — for bobcat (greenhouse cleaning)</t>
+          <t>ELEC-05 — PLC x2 Siemens S7-1200 (64 DI/32 DO/16 AI each)</t>
         </is>
       </c>
       <c r="B116" s="46" t="n">
-        <v>6500</v>
+        <v>14000</v>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>Mobile Equipment Subtotal</t>
-        </is>
-      </c>
-      <c r="B117" s="22">
-        <f>SUM(B101:B116)</f>
-        <v/>
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>ELEC-06 — HMI Touchscreens x2 (15in IP65, SCADA-ready)</t>
+        </is>
+      </c>
+      <c r="B117" s="46" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>ELEC-07 — Cable Tray, Cabling, Earthing (full facility lump sum)</t>
+        </is>
+      </c>
+      <c r="B118" s="46" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>STAFFING — FULL HEADCOUNT &amp; LABOUR COST</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="n"/>
-      <c r="C119" s="3" t="n"/>
-      <c r="D119" s="3" t="n"/>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n"/>
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>ELEC-08 — Compressed Air System (2x15kW screw compressors + ring main)</t>
+        </is>
+      </c>
+      <c r="B119" s="46" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>Headcount</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>Salary (USD/month)</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>Monthly Cost (USD)</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>ELEC-09 — CCTV System (8 cameras 1080p, 30-day NVR)</t>
+        </is>
+      </c>
+      <c r="B120" s="46" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>S1 — EFB Line Operator (shredder + hammer mill)</t>
-        </is>
-      </c>
-      <c r="B121" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C121" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D121" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E121" s="22">
-        <f>B121*C121</f>
-        <v/>
-      </c>
-      <c r="F121" s="54" t="inlineStr">
-        <is>
-          <t>1 per shift, monitors feed + oversize return</t>
+          <t>ELEC-10 — Instrumentation (3 weighbridges + moisture sensors)</t>
+        </is>
+      </c>
+      <c r="B121" s="46" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
-        <is>
-          <t>S1 — EFB Conveyor / Screen Operator</t>
-        </is>
-      </c>
-      <c r="B122" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C122" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D122" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E122" s="22">
-        <f>B122*C122</f>
-        <v/>
-      </c>
-      <c r="F122" s="54" t="inlineStr">
-        <is>
-          <t>Belt + vibrating screen monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>S1 — EFB Screw Press Operator</t>
-        </is>
-      </c>
-      <c r="B123" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C123" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D123" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E123" s="22">
-        <f>B123*C123</f>
-        <v/>
-      </c>
-      <c r="F123" s="54" t="inlineStr">
-        <is>
-          <t>MC control, filtrate routing</t>
-        </is>
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Electrical Subtotal</t>
+        </is>
+      </c>
+      <c r="B122" s="22">
+        <f>SUM(B112:B121)</f>
+        <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>S1 — OPDC Line Operator (shredder + hammer mill)</t>
-        </is>
-      </c>
-      <c r="B124" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C124" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D124" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E124" s="22">
-        <f>B124*C124</f>
-        <v/>
-      </c>
-      <c r="F124" s="54" t="inlineStr"/>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>FIRE PROTECTION — ADDITIONAL (NOT in A8, DATA GAP — RFQ required)</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n"/>
+      <c r="C124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="10" t="inlineStr">
-        <is>
-          <t>S1 — OPDC Conveyor / Press Operator</t>
-        </is>
-      </c>
-      <c r="B125" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C125" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D125" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E125" s="22">
-        <f>B125*C125</f>
-        <v/>
-      </c>
-      <c r="F125" s="54" t="inlineStr"/>
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>S1 — POS Decanter Operator</t>
+          <t>FIRE-HYDRANT-01 — Fire Hydrant Network (100mm mains, 16 bar) DATA GAP RFQ</t>
         </is>
       </c>
       <c r="B126" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="46" t="n">
-        <v>550</v>
-      </c>
-      <c r="D126" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E126" s="22">
-        <f>B126*C126</f>
-        <v/>
-      </c>
-      <c r="F126" s="54" t="inlineStr">
-        <is>
-          <t>Skilled: centrifuge operation + Fe gate sampling</t>
+        <v>20000</v>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Fire/DATA GAP</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>S1 — Wheel Loader Operator (EFB/OPDC feed)</t>
+          <t>FIRE-ALARM-01 — Fire Alarm System (detectors, panel, sirens) DATA GAP</t>
         </is>
       </c>
       <c r="B127" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C127" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D127" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E127" s="22">
-        <f>B127*C127</f>
-        <v/>
-      </c>
-      <c r="F127" s="54" t="inlineStr">
-        <is>
-          <t>Komatsu WA100</t>
+        <v>12000</v>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>Fire/DATA GAP</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>S1 — Dump Truck Driver (mill to S1)</t>
+          <t>FIRE-SUPPRESS-01 — Building Fire Suppression S1 (sprinkler/CO2) DATA GAP</t>
         </is>
       </c>
       <c r="B128" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C128" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D128" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E128" s="22">
-        <f>B128*C128</f>
-        <v/>
-      </c>
-      <c r="F128" s="54" t="inlineStr">
-        <is>
-          <t>2x 10t dump trucks</t>
+        <v>35000</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Fire/DATA GAP</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="10" t="inlineStr">
-        <is>
-          <t>S2 — Chemical Dosing Operator</t>
-        </is>
-      </c>
-      <c r="B129" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C129" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D129" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E129" s="22">
-        <f>B129*C129</f>
-        <v/>
-      </c>
-      <c r="F129" s="54" t="inlineStr">
-        <is>
-          <t>PKSA/chemical mixing, pH monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="10" t="inlineStr">
-        <is>
-          <t>S2 — Neutralisation Bay Attendant</t>
-        </is>
-      </c>
-      <c r="B130" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C130" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D130" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E130" s="22">
-        <f>B130*C130</f>
-        <v/>
-      </c>
-      <c r="F130" s="54" t="inlineStr">
-        <is>
-          <t>Turnings at 8-12hr and 16-20hr</t>
-        </is>
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Fire Protection Additional Subtotal</t>
+        </is>
+      </c>
+      <c r="B129" s="22">
+        <f>SUM(B126:B128)</f>
+        <v/>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>S3 — Biological Inoculation Technician</t>
-        </is>
-      </c>
-      <c r="B131" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="46" t="n">
-        <v>600</v>
-      </c>
-      <c r="D131" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E131" s="22">
-        <f>B131*C131</f>
-        <v/>
-      </c>
-      <c r="F131" s="54" t="inlineStr">
-        <is>
-          <t>Consortium preparation, spray application</t>
-        </is>
-      </c>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>BSF GREENHOUSE + IoT + AUTOMATION (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n"/>
+      <c r="C131" s="3" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>S3 — Composting / Windrow Operator</t>
-        </is>
-      </c>
-      <c r="B132" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C132" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D132" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E132" s="22">
-        <f>B132*C132</f>
-        <v/>
-      </c>
-      <c r="F132" s="54" t="inlineStr">
-        <is>
-          <t>Windrow turner + aeration monitoring</t>
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>S3 — Bobcat Operator (substrate handling)</t>
-        </is>
-      </c>
-      <c r="B133" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C133" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D133" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E133" s="22">
-        <f>B133*C133</f>
-        <v/>
-      </c>
-      <c r="F133" s="54" t="inlineStr">
-        <is>
-          <t>S650 skid-steer</t>
+          <t>Greenhouse Structure — Steel frame, poly-carbonate panels (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B133" s="46" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>S4 — Greenhouse Supervisor</t>
-        </is>
-      </c>
-      <c r="B134" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="46" t="n">
-        <v>900</v>
-      </c>
-      <c r="D134" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E134" s="22">
-        <f>B134*C134</f>
-        <v/>
-      </c>
-      <c r="F134" s="54" t="inlineStr">
-        <is>
-          <t>Overall BSF rearing management</t>
+          <t>Greenhouse Foundation — Concrete slab + drainage (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B134" s="46" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>S4 — BSF Tray Attendant (feeding + monitoring)</t>
-        </is>
-      </c>
-      <c r="B135" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="C135" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D135" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E135" s="22">
-        <f>B135*C135</f>
-        <v/>
-      </c>
-      <c r="F135" s="54" t="inlineStr">
-        <is>
-          <t>4 per shift, 5000m2 per attendant</t>
+          <t>Internal Partition Walls — BSF zone separation (40 bays x 500m2)</t>
+        </is>
+      </c>
+      <c r="B135" s="46" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>S4 — BSF Neonate Nursery Technician</t>
-        </is>
-      </c>
-      <c r="B136" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C136" s="46" t="n">
-        <v>550</v>
-      </c>
-      <c r="D136" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E136" s="22">
-        <f>B136*C136</f>
-        <v/>
-      </c>
-      <c r="F136" s="54" t="inlineStr">
-        <is>
-          <t>Colony management, egg collection</t>
+          <t>Rearing Tray System — Stacked 3-tier racks (20,000 m2 effective)</t>
+        </is>
+      </c>
+      <c r="B136" s="46" t="n">
+        <v>350000</v>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>S4 — Greenhouse Climate / IoT Technician</t>
-        </is>
-      </c>
-      <c r="B137" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="46" t="n">
-        <v>700</v>
-      </c>
-      <c r="D137" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E137" s="22">
-        <f>B137*C137</f>
-        <v/>
-      </c>
-      <c r="F137" s="54" t="inlineStr">
-        <is>
-          <t>SCADA/PLC, sensor maintenance</t>
+          <t>Blackout System — UV-blocking curtains + light baffles</t>
+        </is>
+      </c>
+      <c r="B137" s="46" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>S4 — Bobcat Operator (greenhouse internal)</t>
-        </is>
-      </c>
-      <c r="B138" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C138" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D138" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E138" s="22">
-        <f>B138*C138</f>
-        <v/>
-      </c>
-      <c r="F138" s="54" t="inlineStr">
-        <is>
-          <t>S450, substrate + frass movement</t>
+          <t>HVAC System — Evaporative cooling + exhaust fans (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B138" s="46" t="n">
+        <v>280000</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>S4 — Forklift Operator (greenhouse)</t>
-        </is>
-      </c>
-      <c r="B139" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C139" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D139" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E139" s="22">
-        <f>B139*C139</f>
-        <v/>
-      </c>
-      <c r="F139" s="54" t="inlineStr">
-        <is>
-          <t>1.5t electric forklifts</t>
+          <t>Heating System — Hot water pipes from mill waste heat</t>
+        </is>
+      </c>
+      <c r="B139" s="46" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>S5A — Frass Screening / Bagging Operator</t>
-        </is>
-      </c>
-      <c r="B140" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C140" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D140" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E140" s="22">
-        <f>B140*C140</f>
-        <v/>
-      </c>
-      <c r="F140" s="54" t="inlineStr"/>
+          <t>Humidification System — Fogging nozzles + RH control</t>
+        </is>
+      </c>
+      <c r="B140" s="46" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>S5B — Larvae Separation Operator</t>
-        </is>
-      </c>
-      <c r="B141" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C141" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D141" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E141" s="22">
-        <f>B141*C141</f>
-        <v/>
-      </c>
-      <c r="F141" s="54" t="inlineStr">
-        <is>
-          <t>Vibrating separator + thermal</t>
+          <t>Air Circulation Fans — 120 units, ceiling mount</t>
+        </is>
+      </c>
+      <c r="B141" s="46" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>S5B — Oil Press / Dryer Operator</t>
-        </is>
-      </c>
-      <c r="B142" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C142" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D142" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E142" s="22">
-        <f>B142*C142</f>
-        <v/>
-      </c>
-      <c r="F142" s="54" t="inlineStr">
-        <is>
-          <t>Screw press + belt dryer</t>
+          <t>IoT Temperature Sensors — 200 units (5 per bay, wireless)</t>
+        </is>
+      </c>
+      <c r="B142" s="46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Warehouse — Forklift Operator</t>
-        </is>
-      </c>
-      <c r="B143" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C143" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D143" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E143" s="22">
-        <f>B143*C143</f>
-        <v/>
-      </c>
-      <c r="F143" s="54" t="inlineStr">
-        <is>
-          <t>3t diesel forklift</t>
+          <t>IoT Humidity Sensors — 200 units (5 per bay, wireless)</t>
+        </is>
+      </c>
+      <c r="B143" s="46" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>Warehouse — Storeman / Inventory</t>
-        </is>
-      </c>
-      <c r="B144" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D144" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E144" s="22">
-        <f>B144*C144</f>
-        <v/>
-      </c>
-      <c r="F144" s="54" t="inlineStr">
-        <is>
-          <t>Stock control, dispatch</t>
+          <t>IoT CO2 Sensors — 40 units (1 per bay)</t>
+        </is>
+      </c>
+      <c r="B144" s="46" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>Logistics — Flatbed Truck Driver</t>
-        </is>
-      </c>
-      <c r="B145" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D145" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E145" s="22">
-        <f>B145*C145</f>
-        <v/>
-      </c>
-      <c r="F145" s="54" t="inlineStr">
-        <is>
-          <t>Product delivery</t>
+          <t>IoT pH Sensors — substrate monitoring, 80 units</t>
+        </is>
+      </c>
+      <c r="B145" s="46" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>Logistics — Tanker Truck Driver</t>
-        </is>
-      </c>
-      <c r="B146" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D146" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E146" s="22">
-        <f>B146*C146</f>
-        <v/>
-      </c>
-      <c r="F146" s="54" t="inlineStr">
-        <is>
-          <t>Water/POME</t>
+          <t>IoT Weight Sensors — tray scales for yield tracking, 200 units</t>
+        </is>
+      </c>
+      <c r="B146" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="B147" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="46" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D147" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E147" s="22">
-        <f>B147*C147</f>
-        <v/>
-      </c>
-      <c r="F147" s="54" t="inlineStr">
-        <is>
-          <t>Overall plant management</t>
+          <t>IoT Ammonia Sensors — 40 units (1 per bay)</t>
+        </is>
+      </c>
+      <c r="B147" s="46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>Production Supervisor (S1-S3)</t>
-        </is>
-      </c>
-      <c r="B148" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D148" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E148" s="22">
-        <f>B148*C148</f>
-        <v/>
-      </c>
-      <c r="F148" s="54" t="inlineStr">
-        <is>
-          <t>Preprocessing + treatment</t>
+          <t>Central IoT Gateway — LoRaWAN/WiFi hub + cloud dashboard</t>
+        </is>
+      </c>
+      <c r="B148" s="46" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>Quality Control / Lab Technician</t>
-        </is>
-      </c>
-      <c r="B149" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C149" s="46" t="n">
-        <v>650</v>
-      </c>
-      <c r="D149" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E149" s="22">
-        <f>B149*C149</f>
-        <v/>
-      </c>
-      <c r="F149" s="54" t="inlineStr">
-        <is>
-          <t>pH, MC, ICP-OES, sampling</t>
+          <t>IoT Software Platform — Dashboard, alerts, analytics (annual license)</t>
+        </is>
+      </c>
+      <c r="B149" s="46" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>Maintenance Technician (mechanical)</t>
-        </is>
-      </c>
-      <c r="B150" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C150" s="46" t="n">
-        <v>600</v>
-      </c>
-      <c r="D150" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E150" s="22">
-        <f>B150*C150</f>
-        <v/>
-      </c>
-      <c r="F150" s="54" t="inlineStr">
-        <is>
-          <t>All mechanical equipment</t>
+          <t>Automated Feed Distribution System — conveyor + metering</t>
+        </is>
+      </c>
+      <c r="B150" s="46" t="n">
+        <v>180000</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Automation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>Maintenance Technician (electrical/IoT)</t>
-        </is>
-      </c>
-      <c r="B151" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C151" s="46" t="n">
-        <v>650</v>
-      </c>
-      <c r="D151" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E151" s="22">
-        <f>B151*C151</f>
-        <v/>
-      </c>
-      <c r="F151" s="54" t="inlineStr">
-        <is>
-          <t>Electrical, sensors, PLC</t>
+          <t>Automated Larvae Harvesting System — vibrating separator + conveyor</t>
+        </is>
+      </c>
+      <c r="B151" s="46" t="n">
+        <v>220000</v>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Automation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>HSE Officer</t>
-        </is>
-      </c>
-      <c r="B152" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="46" t="n">
-        <v>700</v>
-      </c>
-      <c r="D152" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E152" s="22">
-        <f>B152*C152</f>
-        <v/>
-      </c>
-      <c r="F152" s="54" t="inlineStr">
-        <is>
-          <t>Safety, PPE, NaOH handling</t>
+          <t>Automated Tray Washing Station</t>
+        </is>
+      </c>
+      <c r="B152" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Automation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>Admin / Finance</t>
-        </is>
-      </c>
-      <c r="B153" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C153" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D153" s="53" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E153" s="22">
-        <f>B153*C153</f>
-        <v/>
-      </c>
-      <c r="F153" s="54" t="inlineStr"/>
+          <t>Automated Climate Control PLC — Siemens/Allen-Bradley</t>
+        </is>
+      </c>
+      <c r="B153" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>Security (gate + night)</t>
-        </is>
-      </c>
-      <c r="B154" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="C154" s="46" t="n">
-        <v>350</v>
-      </c>
-      <c r="D154" s="53" t="inlineStr">
-        <is>
-          <t>3-shift</t>
-        </is>
-      </c>
-      <c r="E154" s="22">
-        <f>B154*C154</f>
-        <v/>
-      </c>
-      <c r="F154" s="54" t="inlineStr">
-        <is>
-          <t>24/7 coverage</t>
+          <t>SCADA System — Central control room, 4 screens</t>
+        </is>
+      </c>
+      <c r="B154" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>Cleaner / General Labour</t>
-        </is>
-      </c>
-      <c r="B155" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="C155" s="46" t="n">
-        <v>350</v>
-      </c>
-      <c r="D155" s="53" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E155" s="22">
-        <f>B155*C155</f>
-        <v/>
-      </c>
-      <c r="F155" s="54" t="inlineStr">
-        <is>
-          <t>Site-wide</t>
+          <t>Water Supply System — treatment + distribution (20,000 m2)</t>
+        </is>
+      </c>
+      <c r="B155" s="46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL STAFFING</t>
-        </is>
-      </c>
-      <c r="B156" s="55">
-        <f>SUM(B121:B155)</f>
-        <v/>
-      </c>
-      <c r="E156" s="51">
-        <f>SUM(E121:E155)</f>
-        <v/>
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>Electrical Distribution — panels, cabling, backup genset</t>
+        </is>
+      </c>
+      <c r="B156" s="46" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>ANNUAL LABOUR COST (x12 months)</t>
-        </is>
-      </c>
-      <c r="E157" s="22">
-        <f>E156*12</f>
-        <v/>
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>Waste Water Treatment — effluent from rearing</t>
+        </is>
+      </c>
+      <c r="B157" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>Fire Suppression System</t>
+        </is>
+      </c>
+      <c r="B158" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL CAPEX SUMMARY</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="n"/>
-      <c r="C159" s="3" t="n"/>
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t>Site Clearing &amp; Grading (2.5 ha total footprint)</t>
+        </is>
+      </c>
+      <c r="B159" s="46" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="38" t="inlineStr">
-        <is>
-          <t>TOTAL CAPEX</t>
-        </is>
-      </c>
-      <c r="B160" s="51">
-        <f>IFERROR(SUM(B5:B159),0)</f>
-        <v/>
+      <c r="A160" s="10" t="inlineStr">
+        <is>
+          <t>Access Roads — Internal + connection to mill (500m gravel)</t>
+        </is>
+      </c>
+      <c r="B160" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>Perimeter Fencing + Security</t>
+        </is>
+      </c>
+      <c r="B161" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="n"/>
-      <c r="C162" s="3" t="n"/>
-      <c r="D162" s="3" t="n"/>
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>Drainage System — Surface + subsurface</t>
+        </is>
+      </c>
+      <c r="B162" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>Cost Item</t>
-        </is>
-      </c>
-      <c r="B163" s="9" t="inlineStr">
-        <is>
-          <t>Monthly Cost (USD)</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>Landscaping + Erosion Control</t>
+        </is>
+      </c>
+      <c r="B163" s="46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Site Works</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="10" t="inlineStr">
         <is>
-          <t>Chemical Treatment</t>
-        </is>
-      </c>
-      <c r="B164" s="22">
-        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 2</t>
+          <t>Staff Facilities — Office, changing rooms, canteen</t>
+        </is>
+      </c>
+      <c r="B164" s="46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>Biological Treatment</t>
-        </is>
-      </c>
-      <c r="B165" s="22">
-        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 3</t>
+          <t>Storage Warehouse — Finished product (500 m2)</t>
+        </is>
+      </c>
+      <c r="B165" s="46" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="10" t="inlineStr">
-        <is>
-          <t>BSF Neonates</t>
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>Greenhouse + IoT Subtotal</t>
         </is>
       </c>
       <c r="B166" s="22">
-        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
-        <v/>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="10" t="inlineStr">
-        <is>
-          <t>Processing (S5B)</t>
-        </is>
-      </c>
-      <c r="B167" s="22">
-        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
-        <v/>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 5B</t>
-        </is>
+        <f>SUM(B133:B165)</f>
+        <v/>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="10" t="inlineStr">
-        <is>
-          <t>Energy / Utilities</t>
-        </is>
-      </c>
-      <c r="B168" s="22">
-        <f>IFERROR(S1_Preprocessing!B30,0)</f>
-        <v/>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 1</t>
-        </is>
-      </c>
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>S5 EXTRACTION &amp; POST-PROCESSING</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n"/>
+      <c r="C168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>Labour (full staffing)</t>
-        </is>
-      </c>
-      <c r="B169" s="22">
-        <f>E156</f>
-        <v/>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>67 staff — see staffing section row 156</t>
+          <t>S5A — Frass screening/bagging line</t>
+        </is>
+      </c>
+      <c r="B169" s="46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>Maintenance (2% CAPEX/month)</t>
-        </is>
-      </c>
-      <c r="B170" s="22">
-        <f>IFERROR(B160*0.02/12,0)</f>
-        <v/>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Industry standard</t>
+          <t>S5B — Larvae separation (vibrating + thermal)</t>
+        </is>
+      </c>
+      <c r="B170" s="46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>Quality Control / Lab</t>
+          <t>S5B — Oil press (screw type, 85% eff)</t>
         </is>
       </c>
       <c r="B171" s="46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Monthly QC testing</t>
+        <v>45000</v>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
+          <t>S5B — Drying system (belt dryer)</t>
+        </is>
+      </c>
+      <c r="B172" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="inlineStr">
+        <is>
+          <t>Laboratory — QC lab (ICP-OES capable)</t>
+        </is>
+      </c>
+      <c r="B173" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>S5 Subtotal</t>
+        </is>
+      </c>
+      <c r="B174" s="22">
+        <f>SUM(B169:B173)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>MOBILE EQUIPMENT &amp; VEHICLES</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n"/>
+      <c r="C176" s="3" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>Wheel Loader — Komatsu WA100 or equiv (1.0m3 bucket, EFB/OPDC handling)</t>
+        </is>
+      </c>
+      <c r="B178" s="46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="inlineStr">
+        <is>
+          <t>Wheel Loader — Komatsu WA70 or equiv (0.5m3 bucket, PKSA/compost)</t>
+        </is>
+      </c>
+      <c r="B179" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="inlineStr">
+        <is>
+          <t>Skid-Steer Loader / Bobcat — S650 or equiv (BSF frass, substrate)</t>
+        </is>
+      </c>
+      <c r="B180" s="46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="10" t="inlineStr">
+        <is>
+          <t>Skid-Steer Loader / Bobcat — S450 or equiv (greenhouse internal)</t>
+        </is>
+      </c>
+      <c r="B181" s="46" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>Mini Excavator — 3.5t (site maintenance, drainage, pit cleaning)</t>
+        </is>
+      </c>
+      <c r="B182" s="46" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="inlineStr">
+        <is>
+          <t>Dump Truck — 10t (EFB transport mill to S1, internal)</t>
+        </is>
+      </c>
+      <c r="B183" s="46" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>Dump Truck — 10t (OPDC/POS transport mill to S1)</t>
+        </is>
+      </c>
+      <c r="B184" s="46" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="inlineStr">
+        <is>
+          <t>Flatbed Truck — 8t (finished product transport, frass/meal)</t>
+        </is>
+      </c>
+      <c r="B185" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="inlineStr">
+        <is>
+          <t>Tanker Truck — 5,000L (water, POME, liquid transfer)</t>
+        </is>
+      </c>
+      <c r="B186" s="46" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="inlineStr">
+        <is>
+          <t>Pickup Truck — 4x4 (site management, 2 units)</t>
+        </is>
+      </c>
+      <c r="B187" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="inlineStr">
+        <is>
+          <t>Forklift — 3t diesel (warehouse, bagged product, 2 units)</t>
+        </is>
+      </c>
+      <c r="B188" s="46" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="inlineStr">
+        <is>
+          <t>Forklift — 1.5t electric (greenhouse internal, 2 units)</t>
+        </is>
+      </c>
+      <c r="B189" s="46" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="inlineStr">
+        <is>
+          <t>Tipping Trailer — 8t (substrate/frass haulage, 2 units)</t>
+        </is>
+      </c>
+      <c r="B190" s="46" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="inlineStr">
+        <is>
+          <t>Pallet Jacks — manual (4 units, warehouse)</t>
+        </is>
+      </c>
+      <c r="B191" s="46" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="inlineStr">
+        <is>
+          <t>Grab Bucket Attachment — for wheel loader (EFB)</t>
+        </is>
+      </c>
+      <c r="B192" s="46" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="inlineStr">
+        <is>
+          <t>Sweeper Attachment — for bobcat (greenhouse cleaning)</t>
+        </is>
+      </c>
+      <c r="B193" s="46" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>Mobile Equipment Subtotal</t>
+        </is>
+      </c>
+      <c r="B194" s="22">
+        <f>SUM(B178:B193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>STAFFING — FULL HEADCOUNT &amp; LABOUR COST</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n"/>
+      <c r="C196" s="3" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
+      <c r="F196" s="3" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>Salary (USD/month)</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="E197" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Cost (USD)</t>
+        </is>
+      </c>
+      <c r="F197" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>S1 — EFB Line Operator (shredder + hammer mill)</t>
+        </is>
+      </c>
+      <c r="B198" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C198" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D198" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E198" s="22">
+        <f>B198*C198</f>
+        <v/>
+      </c>
+      <c r="F198" s="55" t="inlineStr">
+        <is>
+          <t>1 per shift, monitors feed + oversize return</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="inlineStr">
+        <is>
+          <t>S1 — EFB Conveyor / Screen Operator</t>
+        </is>
+      </c>
+      <c r="B199" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C199" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D199" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E199" s="22">
+        <f>B199*C199</f>
+        <v/>
+      </c>
+      <c r="F199" s="55" t="inlineStr">
+        <is>
+          <t>Belt + vibrating screen monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>S1 — EFB Screw Press Operator</t>
+        </is>
+      </c>
+      <c r="B200" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C200" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D200" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E200" s="22">
+        <f>B200*C200</f>
+        <v/>
+      </c>
+      <c r="F200" s="55" t="inlineStr">
+        <is>
+          <t>MC control, filtrate routing</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="10" t="inlineStr">
+        <is>
+          <t>S1 — OPDC Line Operator (shredder + hammer mill)</t>
+        </is>
+      </c>
+      <c r="B201" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C201" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D201" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E201" s="22">
+        <f>B201*C201</f>
+        <v/>
+      </c>
+      <c r="F201" s="55" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="inlineStr">
+        <is>
+          <t>S1 — OPDC Conveyor / Press Operator</t>
+        </is>
+      </c>
+      <c r="B202" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C202" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D202" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E202" s="22">
+        <f>B202*C202</f>
+        <v/>
+      </c>
+      <c r="F202" s="55" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="10" t="inlineStr">
+        <is>
+          <t>S1 — POS Decanter Operator</t>
+        </is>
+      </c>
+      <c r="B203" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" s="46" t="n">
+        <v>550</v>
+      </c>
+      <c r="D203" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E203" s="22">
+        <f>B203*C203</f>
+        <v/>
+      </c>
+      <c r="F203" s="55" t="inlineStr">
+        <is>
+          <t>Skilled: centrifuge operation + Fe gate sampling</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="inlineStr">
+        <is>
+          <t>S1 — Wheel Loader Operator (EFB/OPDC feed)</t>
+        </is>
+      </c>
+      <c r="B204" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C204" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D204" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E204" s="22">
+        <f>B204*C204</f>
+        <v/>
+      </c>
+      <c r="F204" s="55" t="inlineStr">
+        <is>
+          <t>Komatsu WA100</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="inlineStr">
+        <is>
+          <t>S1 — Dump Truck Driver (mill to S1)</t>
+        </is>
+      </c>
+      <c r="B205" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C205" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D205" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E205" s="22">
+        <f>B205*C205</f>
+        <v/>
+      </c>
+      <c r="F205" s="55" t="inlineStr">
+        <is>
+          <t>2x 10t dump trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>S2 — Chemical Dosing Operator</t>
+        </is>
+      </c>
+      <c r="B206" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C206" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D206" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E206" s="22">
+        <f>B206*C206</f>
+        <v/>
+      </c>
+      <c r="F206" s="55" t="inlineStr">
+        <is>
+          <t>PKSA/chemical mixing, pH monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="10" t="inlineStr">
+        <is>
+          <t>S2 — Neutralisation Bay Attendant</t>
+        </is>
+      </c>
+      <c r="B207" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C207" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D207" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E207" s="22">
+        <f>B207*C207</f>
+        <v/>
+      </c>
+      <c r="F207" s="55" t="inlineStr">
+        <is>
+          <t>Turnings at 8-12hr and 16-20hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="inlineStr">
+        <is>
+          <t>S3 — Biological Inoculation Technician</t>
+        </is>
+      </c>
+      <c r="B208" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" s="46" t="n">
+        <v>600</v>
+      </c>
+      <c r="D208" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E208" s="22">
+        <f>B208*C208</f>
+        <v/>
+      </c>
+      <c r="F208" s="55" t="inlineStr">
+        <is>
+          <t>Consortium preparation, spray application</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="inlineStr">
+        <is>
+          <t>S3 — Composting / Windrow Operator</t>
+        </is>
+      </c>
+      <c r="B209" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C209" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D209" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E209" s="22">
+        <f>B209*C209</f>
+        <v/>
+      </c>
+      <c r="F209" s="55" t="inlineStr">
+        <is>
+          <t>Windrow turner + aeration monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
+        <is>
+          <t>S3 — Bobcat Operator (substrate handling)</t>
+        </is>
+      </c>
+      <c r="B210" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D210" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E210" s="22">
+        <f>B210*C210</f>
+        <v/>
+      </c>
+      <c r="F210" s="55" t="inlineStr">
+        <is>
+          <t>S650 skid-steer</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Greenhouse Supervisor</t>
+        </is>
+      </c>
+      <c r="B211" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" s="46" t="n">
+        <v>900</v>
+      </c>
+      <c r="D211" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E211" s="22">
+        <f>B211*C211</f>
+        <v/>
+      </c>
+      <c r="F211" s="55" t="inlineStr">
+        <is>
+          <t>Overall BSF rearing management</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
+        <is>
+          <t>S4 — BSF Tray Attendant (feeding + monitoring)</t>
+        </is>
+      </c>
+      <c r="B212" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="C212" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D212" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E212" s="22">
+        <f>B212*C212</f>
+        <v/>
+      </c>
+      <c r="F212" s="55" t="inlineStr">
+        <is>
+          <t>4 per shift, 5000m2 per attendant</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="inlineStr">
+        <is>
+          <t>S4 — BSF Neonate Nursery Technician</t>
+        </is>
+      </c>
+      <c r="B213" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C213" s="46" t="n">
+        <v>550</v>
+      </c>
+      <c r="D213" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E213" s="22">
+        <f>B213*C213</f>
+        <v/>
+      </c>
+      <c r="F213" s="55" t="inlineStr">
+        <is>
+          <t>Colony management, egg collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Greenhouse Climate / IoT Technician</t>
+        </is>
+      </c>
+      <c r="B214" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" s="46" t="n">
+        <v>700</v>
+      </c>
+      <c r="D214" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E214" s="22">
+        <f>B214*C214</f>
+        <v/>
+      </c>
+      <c r="F214" s="55" t="inlineStr">
+        <is>
+          <t>SCADA/PLC, sensor maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Bobcat Operator (greenhouse internal)</t>
+        </is>
+      </c>
+      <c r="B215" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C215" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D215" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E215" s="22">
+        <f>B215*C215</f>
+        <v/>
+      </c>
+      <c r="F215" s="55" t="inlineStr">
+        <is>
+          <t>S450, substrate + frass movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="inlineStr">
+        <is>
+          <t>S4 — Forklift Operator (greenhouse)</t>
+        </is>
+      </c>
+      <c r="B216" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C216" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D216" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E216" s="22">
+        <f>B216*C216</f>
+        <v/>
+      </c>
+      <c r="F216" s="55" t="inlineStr">
+        <is>
+          <t>1.5t electric forklifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="inlineStr">
+        <is>
+          <t>S5A — Frass Screening / Bagging Operator</t>
+        </is>
+      </c>
+      <c r="B217" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C217" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D217" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E217" s="22">
+        <f>B217*C217</f>
+        <v/>
+      </c>
+      <c r="F217" s="55" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>S5B — Larvae Separation Operator</t>
+        </is>
+      </c>
+      <c r="B218" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C218" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D218" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E218" s="22">
+        <f>B218*C218</f>
+        <v/>
+      </c>
+      <c r="F218" s="55" t="inlineStr">
+        <is>
+          <t>Vibrating separator + thermal</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
+          <t>S5B — Oil Press / Dryer Operator</t>
+        </is>
+      </c>
+      <c r="B219" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C219" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D219" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E219" s="22">
+        <f>B219*C219</f>
+        <v/>
+      </c>
+      <c r="F219" s="55" t="inlineStr">
+        <is>
+          <t>Screw press + belt dryer</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t>Warehouse — Forklift Operator</t>
+        </is>
+      </c>
+      <c r="B220" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C220" s="46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D220" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E220" s="22">
+        <f>B220*C220</f>
+        <v/>
+      </c>
+      <c r="F220" s="55" t="inlineStr">
+        <is>
+          <t>3t diesel forklift</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="10" t="inlineStr">
+        <is>
+          <t>Warehouse — Storeman / Inventory</t>
+        </is>
+      </c>
+      <c r="B221" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D221" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E221" s="22">
+        <f>B221*C221</f>
+        <v/>
+      </c>
+      <c r="F221" s="55" t="inlineStr">
+        <is>
+          <t>Stock control, dispatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="10" t="inlineStr">
+        <is>
+          <t>Logistics — Flatbed Truck Driver</t>
+        </is>
+      </c>
+      <c r="B222" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D222" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E222" s="22">
+        <f>B222*C222</f>
+        <v/>
+      </c>
+      <c r="F222" s="55" t="inlineStr">
+        <is>
+          <t>Product delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="inlineStr">
+        <is>
+          <t>Logistics — Tanker Truck Driver</t>
+        </is>
+      </c>
+      <c r="B223" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="D223" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E223" s="22">
+        <f>B223*C223</f>
+        <v/>
+      </c>
+      <c r="F223" s="55" t="inlineStr">
+        <is>
+          <t>Water/POME</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="10" t="inlineStr">
+        <is>
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="B224" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D224" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E224" s="22">
+        <f>B224*C224</f>
+        <v/>
+      </c>
+      <c r="F224" s="55" t="inlineStr">
+        <is>
+          <t>Overall plant management</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="inlineStr">
+        <is>
+          <t>Production Supervisor (S1-S3)</t>
+        </is>
+      </c>
+      <c r="B225" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" s="46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D225" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E225" s="22">
+        <f>B225*C225</f>
+        <v/>
+      </c>
+      <c r="F225" s="55" t="inlineStr">
+        <is>
+          <t>Preprocessing + treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="inlineStr">
+        <is>
+          <t>Quality Control / Lab Technician</t>
+        </is>
+      </c>
+      <c r="B226" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C226" s="46" t="n">
+        <v>650</v>
+      </c>
+      <c r="D226" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E226" s="22">
+        <f>B226*C226</f>
+        <v/>
+      </c>
+      <c r="F226" s="55" t="inlineStr">
+        <is>
+          <t>pH, MC, ICP-OES, sampling</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance Technician (mechanical)</t>
+        </is>
+      </c>
+      <c r="B227" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C227" s="46" t="n">
+        <v>600</v>
+      </c>
+      <c r="D227" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E227" s="22">
+        <f>B227*C227</f>
+        <v/>
+      </c>
+      <c r="F227" s="55" t="inlineStr">
+        <is>
+          <t>All mechanical equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance Technician (electrical/IoT)</t>
+        </is>
+      </c>
+      <c r="B228" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" s="46" t="n">
+        <v>650</v>
+      </c>
+      <c r="D228" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E228" s="22">
+        <f>B228*C228</f>
+        <v/>
+      </c>
+      <c r="F228" s="55" t="inlineStr">
+        <is>
+          <t>Electrical, sensors, PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
+        <is>
+          <t>HSE Officer</t>
+        </is>
+      </c>
+      <c r="B229" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" s="46" t="n">
+        <v>700</v>
+      </c>
+      <c r="D229" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E229" s="22">
+        <f>B229*C229</f>
+        <v/>
+      </c>
+      <c r="F229" s="55" t="inlineStr">
+        <is>
+          <t>Safety, PPE, NaOH handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>Admin / Finance</t>
+        </is>
+      </c>
+      <c r="B230" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C230" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D230" s="54" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E230" s="22">
+        <f>B230*C230</f>
+        <v/>
+      </c>
+      <c r="F230" s="55" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="inlineStr">
+        <is>
+          <t>Security (gate + night)</t>
+        </is>
+      </c>
+      <c r="B231" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C231" s="46" t="n">
+        <v>350</v>
+      </c>
+      <c r="D231" s="54" t="inlineStr">
+        <is>
+          <t>3-shift</t>
+        </is>
+      </c>
+      <c r="E231" s="22">
+        <f>B231*C231</f>
+        <v/>
+      </c>
+      <c r="F231" s="55" t="inlineStr">
+        <is>
+          <t>24/7 coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>Cleaner / General Labour</t>
+        </is>
+      </c>
+      <c r="B232" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C232" s="46" t="n">
+        <v>350</v>
+      </c>
+      <c r="D232" s="54" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E232" s="22">
+        <f>B232*C232</f>
+        <v/>
+      </c>
+      <c r="F232" s="55" t="inlineStr">
+        <is>
+          <t>Site-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL STAFFING</t>
+        </is>
+      </c>
+      <c r="B233" s="56">
+        <f>SUM(B198:B232)</f>
+        <v/>
+      </c>
+      <c r="E233" s="51">
+        <f>SUM(E198:E232)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>ANNUAL LABOUR COST (x12 months)</t>
+        </is>
+      </c>
+      <c r="E234" s="22">
+        <f>E233*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX SUMMARY</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n"/>
+      <c r="C236" s="3" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX</t>
+        </is>
+      </c>
+      <c r="B237" s="51">
+        <f>IFERROR(SUM(B5:B236),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n"/>
+      <c r="C239" s="3" t="n"/>
+      <c r="D239" s="3" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>Cost Item</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="inlineStr">
+        <is>
+          <t>Chemical Treatment</t>
+        </is>
+      </c>
+      <c r="B241" s="22">
+        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
+        <v/>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="inlineStr">
+        <is>
+          <t>Biological Treatment</t>
+        </is>
+      </c>
+      <c r="B242" s="22">
+        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
+        <v/>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="inlineStr">
+        <is>
+          <t>BSF Neonates</t>
+        </is>
+      </c>
+      <c r="B243" s="22">
+        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
+        <v/>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>Processing (S5B)</t>
+        </is>
+      </c>
+      <c r="B244" s="22">
+        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
+        <v/>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>Energy / Utilities</t>
+        </is>
+      </c>
+      <c r="B245" s="22">
+        <f>IFERROR(S1_Preprocessing!B30,0)</f>
+        <v/>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="inlineStr">
+        <is>
+          <t>Labour (full staffing)</t>
+        </is>
+      </c>
+      <c r="B246" s="22">
+        <f>E233</f>
+        <v/>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>67 staff — see staffing section row 233</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance (2% CAPEX/month)</t>
+        </is>
+      </c>
+      <c r="B247" s="22">
+        <f>IFERROR(B237*0.02/12,0)</f>
+        <v/>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Industry standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="inlineStr">
+        <is>
+          <t>Quality Control / Lab</t>
+        </is>
+      </c>
+      <c r="B248" s="46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Monthly QC testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="inlineStr">
+        <is>
           <t>Transport / Logistics</t>
         </is>
       </c>
-      <c r="B172" s="46" t="n">
+      <c r="B249" s="46" t="n">
         <v>3000</v>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
         <is>
           <t>Product distribution</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="38" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="38" t="inlineStr">
         <is>
           <t>TOTAL MONTHLY OPEX</t>
         </is>
       </c>
-      <c r="B173" s="52">
-        <f>IFERROR(SUM(B164:B172),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
+      <c r="B250" s="52">
+        <f>IFERROR(SUM(B241:B249),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
         <is>
           <t>PAYBACK &amp; NPV ANALYSIS</t>
         </is>
       </c>
-      <c r="B175" s="3" t="n"/>
-      <c r="C175" s="3" t="n"/>
-      <c r="D175" s="3" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="B252" s="3" t="n"/>
+      <c r="C252" s="3" t="n"/>
+      <c r="D252" s="3" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
         <is>
           <t>Total CAPEX</t>
         </is>
       </c>
-      <c r="B176" s="22">
-        <f>B160</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="B253" s="22">
+        <f>B237</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
         <is>
           <t>Monthly Gross Profit</t>
         </is>
       </c>
-      <c r="B177" s="22">
-        <f>IFERROR(Summary_Dashboard!B24-B173,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="38" t="inlineStr">
+      <c r="B254" s="22">
+        <f>IFERROR(Summary_Dashboard!B24-B250,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="38" t="inlineStr">
         <is>
           <t>Payback Period (months)</t>
         </is>
       </c>
-      <c r="B178" s="42">
-        <f>IFERROR(B176/B177,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
+      <c r="B255" s="42">
+        <f>IFERROR(B253/B254,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>Payback Period (years)</t>
         </is>
       </c>
-      <c r="B179" s="13">
-        <f>IFERROR(B178/12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
+      <c r="B256" s="13">
+        <f>IFERROR(B255/12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>IRR Discount Rate (user-adjustable)</t>
         </is>
       </c>
-      <c r="B181" s="56" t="n">
+      <c r="B258" s="57" t="n">
         <v>0.12</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
         <is>
           <t>Annual Net Cash Flow</t>
         </is>
       </c>
-      <c r="B182" s="22">
-        <f>IFERROR(B177*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="7" t="inlineStr">
+      <c r="B259" s="22">
+        <f>IFERROR(B254*12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="7" t="inlineStr">
         <is>
           <t>5-Year NPV (simple estimate)</t>
         </is>
       </c>
-      <c r="B183" s="30">
-        <f>IFERROR(B182/(1+B181)^1+B182/(1+B181)^2+B182/(1+B181)^3+B182/(1+B181)^4+B182/(1+B181)^5-B176,0)</f>
+      <c r="B260" s="30">
+        <f>IFERROR(B259/(1+B258)^1+B259/(1+B258)^2+B259/(1+B258)^3+B259/(1+B258)^4+B259/(1+B258)^5-B253,0)</f>
         <v/>
       </c>
     </row>

--- a/CFI_Master_Excel.xlsx
+++ b/CFI_Master_Excel.xlsx
@@ -140,7 +140,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -175,12 +175,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FF4444"/>
         <bgColor rgb="00FF4444"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCCCC"/>
-        <bgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -254,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -356,7 +350,6 @@
     <xf numFmtId="167" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4556,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -6021,7 +6014,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>ELECTRICAL PANELS &amp; CONTROLS (10 items, $227,500 — CAPEX v4.1)</t>
+          <t>ELECTRICAL PANELS &amp; CONTROLS (11 items, $282,500 — CAPEX v4.1 + GH est.)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n"/>
@@ -6195,147 +6188,147 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>GH-ELEC — Greenhouse Internal Electrical (SCADA, sensors, zone controls) est.</t>
+        </is>
+      </c>
+      <c r="B122" s="46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>Electrical Subtotal</t>
         </is>
       </c>
-      <c r="B122" s="22">
-        <f>SUM(B112:B121)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>FIRE PROTECTION — ADDITIONAL (NOT in A8, DATA GAP — RFQ required)</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="n"/>
-      <c r="C124" s="3" t="n"/>
+      <c r="B123" s="22">
+        <f>SUM(B112:B122)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>FIRE PROTECTION — ADDITIONAL (NOT in A8, estimated)</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n"/>
+      <c r="C125" s="3" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>Equipment / Item</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
         <is>
           <t>Estimated Cost (USD)</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t>FIRE-HYDRANT-01 — Fire Hydrant Network (100mm mains, 16 bar) DATA GAP RFQ</t>
-        </is>
-      </c>
-      <c r="B126" s="53" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>Fire/DATA GAP</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>FIRE-ALARM-01 — Fire Alarm System (detectors, panel, sirens) DATA GAP</t>
-        </is>
-      </c>
-      <c r="B127" s="53" t="n">
-        <v>12000</v>
+          <t>FIRE-HYDRANT-01 — Fire Hydrant Network (100mm mains, 16 bar) est.</t>
+        </is>
+      </c>
+      <c r="B127" s="46" t="n">
+        <v>20000</v>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Fire/DATA GAP</t>
+          <t>Fire/Est.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>FIRE-SUPPRESS-01 — Building Fire Suppression S1 (sprinkler/CO2) DATA GAP</t>
-        </is>
-      </c>
-      <c r="B128" s="53" t="n">
+          <t>FIRE-ALARM-01 — Fire Alarm System (detectors, panel, sirens) est.</t>
+        </is>
+      </c>
+      <c r="B128" s="46" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Fire/Est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>FIRE-SUPPRESS-01 — Building Fire Suppression S1 (sprinkler/CO2) est.</t>
+        </is>
+      </c>
+      <c r="B129" s="46" t="n">
         <v>35000</v>
       </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>Fire/DATA GAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Fire/Est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>Fire Protection Additional Subtotal</t>
         </is>
       </c>
-      <c r="B129" s="22">
-        <f>SUM(B126:B128)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="B130" s="22">
+        <f>SUM(B127:B129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>BSF GREENHOUSE + IoT + AUTOMATION (20,000 m2)</t>
         </is>
       </c>
-      <c r="B131" s="3" t="n"/>
-      <c r="C131" s="3" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="B132" s="3" t="n"/>
+      <c r="C132" s="3" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>Equipment / Item</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>Estimated Cost (USD)</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>Greenhouse Structure — Steel frame, poly-carbonate panels (20,000 m2)</t>
-        </is>
-      </c>
-      <c r="B133" s="46" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse Foundation — Concrete slab + drainage (20,000 m2)</t>
+          <t>Greenhouse Structure — Steel frame, poly-carbonate panels (20,000 m2)</t>
         </is>
       </c>
       <c r="B134" s="46" t="n">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
@@ -6346,11 +6339,11 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Internal Partition Walls — BSF zone separation (40 bays x 500m2)</t>
+          <t>Greenhouse Foundation — Concrete slab + drainage (20,000 m2)</t>
         </is>
       </c>
       <c r="B135" s="46" t="n">
-        <v>120000</v>
+        <v>400000</v>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
@@ -6361,11 +6354,11 @@
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>Rearing Tray System — Stacked 3-tier racks (20,000 m2 effective)</t>
+          <t>Internal Partition Walls — BSF zone separation (40 bays x 500m2)</t>
         </is>
       </c>
       <c r="B136" s="46" t="n">
-        <v>350000</v>
+        <v>120000</v>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
@@ -6376,11 +6369,11 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Blackout System — UV-blocking curtains + light baffles</t>
+          <t>Rearing Tray System — Stacked 3-tier racks (20,000 m2 effective)</t>
         </is>
       </c>
       <c r="B137" s="46" t="n">
-        <v>80000</v>
+        <v>350000</v>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
@@ -6391,11 +6384,11 @@
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>HVAC System — Evaporative cooling + exhaust fans (20,000 m2)</t>
+          <t>Blackout System — UV-blocking curtains + light baffles</t>
         </is>
       </c>
       <c r="B138" s="46" t="n">
-        <v>280000</v>
+        <v>80000</v>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
@@ -6406,11 +6399,11 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Heating System — Hot water pipes from mill waste heat</t>
+          <t>HVAC System — Evaporative cooling + exhaust fans (20,000 m2)</t>
         </is>
       </c>
       <c r="B139" s="46" t="n">
-        <v>150000</v>
+        <v>280000</v>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
@@ -6421,11 +6414,11 @@
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>Humidification System — Fogging nozzles + RH control</t>
+          <t>Heating System — Hot water pipes from mill waste heat</t>
         </is>
       </c>
       <c r="B140" s="46" t="n">
-        <v>65000</v>
+        <v>150000</v>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
@@ -6436,11 +6429,11 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Air Circulation Fans — 120 units, ceiling mount</t>
+          <t>Humidification System — Fogging nozzles + RH control</t>
         </is>
       </c>
       <c r="B141" s="46" t="n">
-        <v>48000</v>
+        <v>65000</v>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
@@ -6451,26 +6444,26 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>IoT Temperature Sensors — 200 units (5 per bay, wireless)</t>
+          <t>Air Circulation Fans — 120 units, ceiling mount</t>
         </is>
       </c>
       <c r="B142" s="46" t="n">
-        <v>30000</v>
+        <v>48000</v>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>IoT Humidity Sensors — 200 units (5 per bay, wireless)</t>
+          <t>IoT Temperature Sensors — 200 units (5 per bay, wireless)</t>
         </is>
       </c>
       <c r="B143" s="46" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
@@ -6481,11 +6474,11 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>IoT CO2 Sensors — 40 units (1 per bay)</t>
+          <t>IoT Humidity Sensors — 200 units (5 per bay, wireless)</t>
         </is>
       </c>
       <c r="B144" s="46" t="n">
-        <v>16000</v>
+        <v>25000</v>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
@@ -6496,11 +6489,11 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>IoT pH Sensors — substrate monitoring, 80 units</t>
+          <t>IoT CO2 Sensors — 40 units (1 per bay)</t>
         </is>
       </c>
       <c r="B145" s="46" t="n">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
@@ -6511,11 +6504,11 @@
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>IoT Weight Sensors — tray scales for yield tracking, 200 units</t>
+          <t>IoT pH Sensors — substrate monitoring, 80 units</t>
         </is>
       </c>
       <c r="B146" s="46" t="n">
-        <v>40000</v>
+        <v>24000</v>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
@@ -6526,11 +6519,11 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>IoT Ammonia Sensors — 40 units (1 per bay)</t>
+          <t>IoT Weight Sensors — tray scales for yield tracking, 200 units</t>
         </is>
       </c>
       <c r="B147" s="46" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
@@ -6541,11 +6534,11 @@
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>Central IoT Gateway — LoRaWAN/WiFi hub + cloud dashboard</t>
+          <t>IoT Ammonia Sensors — 40 units (1 per bay)</t>
         </is>
       </c>
       <c r="B148" s="46" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
@@ -6556,11 +6549,11 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>IoT Software Platform — Dashboard, alerts, analytics (annual license)</t>
+          <t>Central IoT Gateway — LoRaWAN/WiFi hub + cloud dashboard</t>
         </is>
       </c>
       <c r="B149" s="46" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
@@ -6571,26 +6564,26 @@
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>Automated Feed Distribution System — conveyor + metering</t>
+          <t>IoT Software Platform — Dashboard, alerts, analytics (annual license)</t>
         </is>
       </c>
       <c r="B150" s="46" t="n">
-        <v>180000</v>
+        <v>25000</v>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>Automated Larvae Harvesting System — vibrating separator + conveyor</t>
+          <t>Automated Feed Distribution System — conveyor + metering</t>
         </is>
       </c>
       <c r="B151" s="46" t="n">
-        <v>220000</v>
+        <v>180000</v>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
@@ -6601,11 +6594,11 @@
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>Automated Tray Washing Station</t>
+          <t>Automated Larvae Harvesting System — vibrating separator + conveyor</t>
         </is>
       </c>
       <c r="B152" s="46" t="n">
-        <v>45000</v>
+        <v>220000</v>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
@@ -6616,26 +6609,26 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>Automated Climate Control PLC — Siemens/Allen-Bradley</t>
+          <t>Automated Tray Washing Station</t>
         </is>
       </c>
       <c r="B153" s="46" t="n">
-        <v>35000</v>
+        <v>45000</v>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>IoT/Automation</t>
+          <t>Automation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>SCADA System — Central control room, 4 screens</t>
+          <t>Automated Climate Control PLC — Siemens/Allen-Bradley</t>
         </is>
       </c>
       <c r="B154" s="46" t="n">
-        <v>40000</v>
+        <v>35000</v>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
@@ -6646,26 +6639,26 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>Water Supply System — treatment + distribution (20,000 m2)</t>
+          <t>SCADA System — Central control room, 4 screens</t>
         </is>
       </c>
       <c r="B155" s="46" t="n">
-        <v>85000</v>
+        <v>40000</v>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>IoT/Automation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>Electrical Distribution — panels, cabling, backup genset</t>
+          <t>Water Supply System — treatment + distribution (20,000 m2)</t>
         </is>
       </c>
       <c r="B156" s="46" t="n">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
@@ -6676,11 +6669,11 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>Waste Water Treatment — effluent from rearing</t>
+          <t>Electrical Distribution — panels, cabling, backup genset</t>
         </is>
       </c>
       <c r="B157" s="46" t="n">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
@@ -6691,41 +6684,41 @@
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>Fire Suppression System</t>
+          <t>Waste Water Treatment — effluent from rearing</t>
         </is>
       </c>
       <c r="B158" s="46" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>Site Clearing &amp; Grading (2.5 ha total footprint)</t>
+          <t>Fire Suppression System</t>
         </is>
       </c>
       <c r="B159" s="46" t="n">
-        <v>80000</v>
+        <v>45000</v>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Site Works</t>
+          <t>Facilities</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>Access Roads — Internal + connection to mill (500m gravel)</t>
+          <t>Site Clearing &amp; Grading (2.5 ha total footprint)</t>
         </is>
       </c>
       <c r="B160" s="46" t="n">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
@@ -6736,41 +6729,41 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>Perimeter Fencing + Security</t>
+          <t>Access Roads — Internal + connection to mill (500m gravel)</t>
         </is>
       </c>
       <c r="B161" s="46" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Site Works</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>Drainage System — Surface + subsurface</t>
+          <t>Perimeter Fencing + Security</t>
         </is>
       </c>
       <c r="B162" s="46" t="n">
-        <v>55000</v>
+        <v>35000</v>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Site Works</t>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>Landscaping + Erosion Control</t>
+          <t>Drainage System — Surface + subsurface</t>
         </is>
       </c>
       <c r="B163" s="46" t="n">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
@@ -6781,76 +6774,76 @@
     <row r="164">
       <c r="A164" s="10" t="inlineStr">
         <is>
-          <t>Staff Facilities — Office, changing rooms, canteen</t>
+          <t>Landscaping + Erosion Control</t>
         </is>
       </c>
       <c r="B164" s="46" t="n">
-        <v>85000</v>
+        <v>20000</v>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Site Works</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
+          <t>Staff Facilities — Office, changing rooms, canteen</t>
+        </is>
+      </c>
+      <c r="B165" s="46" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
           <t>Storage Warehouse — Finished product (500 m2)</t>
         </is>
       </c>
-      <c r="B165" s="46" t="n">
+      <c r="B166" s="46" t="n">
         <v>120000</v>
       </c>
-      <c r="C165" s="10" t="inlineStr">
+      <c r="C166" s="10" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="7" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>Greenhouse + IoT Subtotal</t>
         </is>
       </c>
-      <c r="B166" s="22">
-        <f>SUM(B133:B165)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
+      <c r="B167" s="22">
+        <f>SUM(B134:B166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>S5 EXTRACTION &amp; POST-PROCESSING</t>
         </is>
       </c>
-      <c r="B168" s="3" t="n"/>
-      <c r="C168" s="3" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="10" t="inlineStr">
-        <is>
-          <t>S5A — Frass screening/bagging line</t>
-        </is>
-      </c>
-      <c r="B169" s="46" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C169" s="10" t="inlineStr">
-        <is>
-          <t>S5/Lab</t>
-        </is>
-      </c>
+      <c r="B169" s="3" t="n"/>
+      <c r="C169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>S5B — Larvae separation (vibrating + thermal)</t>
+          <t>S5A — Frass screening/bagging line</t>
         </is>
       </c>
       <c r="B170" s="46" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
@@ -6861,11 +6854,11 @@
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>S5B — Oil press (screw type, 85% eff)</t>
+          <t>S5B — Larvae separation (vibrating + thermal)</t>
         </is>
       </c>
       <c r="B171" s="46" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
@@ -6876,11 +6869,11 @@
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>S5B — Drying system (belt dryer)</t>
+          <t>S5B — Oil press (screw type, 85% eff)</t>
         </is>
       </c>
       <c r="B172" s="46" t="n">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
@@ -6891,78 +6884,78 @@
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
+          <t>S5B — Drying system (belt dryer)</t>
+        </is>
+      </c>
+      <c r="B173" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>S5/Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
           <t>Laboratory — QC lab (ICP-OES capable)</t>
         </is>
       </c>
-      <c r="B173" s="46" t="n">
+      <c r="B174" s="46" t="n">
         <v>45000</v>
       </c>
-      <c r="C173" s="10" t="inlineStr">
+      <c r="C174" s="10" t="inlineStr">
         <is>
           <t>S5/Lab</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="7" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t>S5 Subtotal</t>
         </is>
       </c>
-      <c r="B174" s="22">
-        <f>SUM(B169:B173)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
+      <c r="B175" s="22">
+        <f>SUM(B170:B174)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>MOBILE EQUIPMENT &amp; VEHICLES</t>
         </is>
       </c>
-      <c r="B176" s="3" t="n"/>
-      <c r="C176" s="3" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="9" t="inlineStr">
+      <c r="B177" s="3" t="n"/>
+      <c r="C177" s="3" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
         <is>
           <t>Equipment / Item</t>
         </is>
       </c>
-      <c r="B177" s="9" t="inlineStr">
+      <c r="B178" s="9" t="inlineStr">
         <is>
           <t>Estimated Cost (USD)</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="C178" s="9" t="inlineStr">
         <is>
           <t>Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="10" t="inlineStr">
-        <is>
-          <t>Wheel Loader — Komatsu WA100 or equiv (1.0m3 bucket, EFB/OPDC handling)</t>
-        </is>
-      </c>
-      <c r="B178" s="46" t="n">
-        <v>85000</v>
-      </c>
-      <c r="C178" s="10" t="inlineStr">
-        <is>
-          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>Wheel Loader — Komatsu WA70 or equiv (0.5m3 bucket, PKSA/compost)</t>
+          <t>Wheel Loader — Komatsu WA100 or equiv (1.0m3 bucket, EFB/OPDC handling)</t>
         </is>
       </c>
       <c r="B179" s="46" t="n">
-        <v>55000</v>
+        <v>85000</v>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
@@ -6973,11 +6966,11 @@
     <row r="180">
       <c r="A180" s="10" t="inlineStr">
         <is>
-          <t>Skid-Steer Loader / Bobcat — S650 or equiv (BSF frass, substrate)</t>
+          <t>Wheel Loader — Komatsu WA70 or equiv (0.5m3 bucket, PKSA/compost)</t>
         </is>
       </c>
       <c r="B180" s="46" t="n">
-        <v>45000</v>
+        <v>55000</v>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
@@ -6988,11 +6981,11 @@
     <row r="181">
       <c r="A181" s="10" t="inlineStr">
         <is>
-          <t>Skid-Steer Loader / Bobcat — S450 or equiv (greenhouse internal)</t>
+          <t>Skid-Steer Loader / Bobcat — S650 or equiv (BSF frass, substrate)</t>
         </is>
       </c>
       <c r="B181" s="46" t="n">
-        <v>38000</v>
+        <v>45000</v>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
@@ -7003,11 +6996,11 @@
     <row r="182">
       <c r="A182" s="10" t="inlineStr">
         <is>
-          <t>Mini Excavator — 3.5t (site maintenance, drainage, pit cleaning)</t>
+          <t>Skid-Steer Loader / Bobcat — S450 or equiv (greenhouse internal)</t>
         </is>
       </c>
       <c r="B182" s="46" t="n">
-        <v>42000</v>
+        <v>38000</v>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
@@ -7018,11 +7011,11 @@
     <row r="183">
       <c r="A183" s="10" t="inlineStr">
         <is>
-          <t>Dump Truck — 10t (EFB transport mill to S1, internal)</t>
+          <t>Mini Excavator — 3.5t (site maintenance, drainage, pit cleaning)</t>
         </is>
       </c>
       <c r="B183" s="46" t="n">
-        <v>65000</v>
+        <v>42000</v>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
@@ -7033,7 +7026,7 @@
     <row r="184">
       <c r="A184" s="10" t="inlineStr">
         <is>
-          <t>Dump Truck — 10t (OPDC/POS transport mill to S1)</t>
+          <t>Dump Truck — 10t (EFB transport mill to S1, internal)</t>
         </is>
       </c>
       <c r="B184" s="46" t="n">
@@ -7048,11 +7041,11 @@
     <row r="185">
       <c r="A185" s="10" t="inlineStr">
         <is>
-          <t>Flatbed Truck — 8t (finished product transport, frass/meal)</t>
+          <t>Dump Truck — 10t (OPDC/POS transport mill to S1)</t>
         </is>
       </c>
       <c r="B185" s="46" t="n">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
@@ -7063,11 +7056,11 @@
     <row r="186">
       <c r="A186" s="10" t="inlineStr">
         <is>
-          <t>Tanker Truck — 5,000L (water, POME, liquid transfer)</t>
+          <t>Flatbed Truck — 8t (finished product transport, frass/meal)</t>
         </is>
       </c>
       <c r="B186" s="46" t="n">
-        <v>48000</v>
+        <v>55000</v>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
@@ -7078,11 +7071,11 @@
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>Pickup Truck — 4x4 (site management, 2 units)</t>
+          <t>Tanker Truck — 5,000L (water, POME, liquid transfer)</t>
         </is>
       </c>
       <c r="B187" s="46" t="n">
-        <v>60000</v>
+        <v>48000</v>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
@@ -7093,11 +7086,11 @@
     <row r="188">
       <c r="A188" s="10" t="inlineStr">
         <is>
-          <t>Forklift — 3t diesel (warehouse, bagged product, 2 units)</t>
+          <t>Pickup Truck — 4x4 (site management, 2 units)</t>
         </is>
       </c>
       <c r="B188" s="46" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
@@ -7108,11 +7101,11 @@
     <row r="189">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>Forklift — 1.5t electric (greenhouse internal, 2 units)</t>
+          <t>Forklift — 3t diesel (warehouse, bagged product, 2 units)</t>
         </is>
       </c>
       <c r="B189" s="46" t="n">
-        <v>36000</v>
+        <v>50000</v>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
@@ -7123,11 +7116,11 @@
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
         <is>
-          <t>Tipping Trailer — 8t (substrate/frass haulage, 2 units)</t>
+          <t>Forklift — 1.5t electric (greenhouse internal, 2 units)</t>
         </is>
       </c>
       <c r="B190" s="46" t="n">
-        <v>24000</v>
+        <v>36000</v>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
@@ -7138,11 +7131,11 @@
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>Pallet Jacks — manual (4 units, warehouse)</t>
+          <t>Tipping Trailer — 8t (substrate/frass haulage, 2 units)</t>
         </is>
       </c>
       <c r="B191" s="46" t="n">
-        <v>3200</v>
+        <v>24000</v>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
@@ -7153,11 +7146,11 @@
     <row r="192">
       <c r="A192" s="10" t="inlineStr">
         <is>
-          <t>Grab Bucket Attachment — for wheel loader (EFB)</t>
+          <t>Pallet Jacks — manual (4 units, warehouse)</t>
         </is>
       </c>
       <c r="B192" s="46" t="n">
-        <v>8000</v>
+        <v>3200</v>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
@@ -7168,113 +7161,101 @@
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
         <is>
+          <t>Grab Bucket Attachment — for wheel loader (EFB)</t>
+        </is>
+      </c>
+      <c r="B193" s="46" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="inlineStr">
+        <is>
           <t>Sweeper Attachment — for bobcat (greenhouse cleaning)</t>
         </is>
       </c>
-      <c r="B193" s="46" t="n">
+      <c r="B194" s="46" t="n">
         <v>6500</v>
       </c>
-      <c r="C193" s="10" t="inlineStr">
+      <c r="C194" s="10" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
         <is>
           <t>Mobile Equipment Subtotal</t>
         </is>
       </c>
-      <c r="B194" s="22">
-        <f>SUM(B178:B193)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="3" t="inlineStr">
+      <c r="B195" s="22">
+        <f>SUM(B179:B194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t>STAFFING — FULL HEADCOUNT &amp; LABOUR COST</t>
         </is>
       </c>
-      <c r="B196" s="3" t="n"/>
-      <c r="C196" s="3" t="n"/>
-      <c r="D196" s="3" t="n"/>
-      <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="9" t="inlineStr">
+      <c r="B197" s="3" t="n"/>
+      <c r="C197" s="3" t="n"/>
+      <c r="D197" s="3" t="n"/>
+      <c r="E197" s="3" t="n"/>
+      <c r="F197" s="3" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B197" s="9" t="inlineStr">
+      <c r="B198" s="9" t="inlineStr">
         <is>
           <t>Headcount</t>
         </is>
       </c>
-      <c r="C197" s="9" t="inlineStr">
+      <c r="C198" s="9" t="inlineStr">
         <is>
           <t>Salary (USD/month)</t>
         </is>
       </c>
-      <c r="D197" s="9" t="inlineStr">
+      <c r="D198" s="9" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="E197" s="9" t="inlineStr">
+      <c r="E198" s="9" t="inlineStr">
         <is>
           <t>Monthly Cost (USD)</t>
         </is>
       </c>
-      <c r="F197" s="9" t="inlineStr">
+      <c r="F198" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="10" t="inlineStr">
-        <is>
-          <t>S1 — EFB Line Operator (shredder + hammer mill)</t>
-        </is>
-      </c>
-      <c r="B198" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C198" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D198" s="54" t="inlineStr">
-        <is>
-          <t>2-shift</t>
-        </is>
-      </c>
-      <c r="E198" s="22">
-        <f>B198*C198</f>
-        <v/>
-      </c>
-      <c r="F198" s="55" t="inlineStr">
-        <is>
-          <t>1 per shift, monitors feed + oversize return</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
         <is>
-          <t>S1 — EFB Conveyor / Screen Operator</t>
-        </is>
-      </c>
-      <c r="B199" s="54" t="n">
+          <t>S1 — EFB Line Operator (shredder + hammer mill)</t>
+        </is>
+      </c>
+      <c r="B199" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C199" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D199" s="54" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="D199" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7283,25 +7264,25 @@
         <f>B199*C199</f>
         <v/>
       </c>
-      <c r="F199" s="55" t="inlineStr">
-        <is>
-          <t>Belt + vibrating screen monitoring</t>
+      <c r="F199" s="54" t="inlineStr">
+        <is>
+          <t>1 per shift, monitors feed + oversize return</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="10" t="inlineStr">
         <is>
-          <t>S1 — EFB Screw Press Operator</t>
-        </is>
-      </c>
-      <c r="B200" s="54" t="n">
+          <t>S1 — EFB Conveyor / Screen Operator</t>
+        </is>
+      </c>
+      <c r="B200" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C200" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D200" s="54" t="inlineStr">
+        <v>400</v>
+      </c>
+      <c r="D200" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7310,25 +7291,25 @@
         <f>B200*C200</f>
         <v/>
       </c>
-      <c r="F200" s="55" t="inlineStr">
-        <is>
-          <t>MC control, filtrate routing</t>
+      <c r="F200" s="54" t="inlineStr">
+        <is>
+          <t>Belt + vibrating screen monitoring</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="10" t="inlineStr">
         <is>
-          <t>S1 — OPDC Line Operator (shredder + hammer mill)</t>
-        </is>
-      </c>
-      <c r="B201" s="54" t="n">
+          <t>S1 — EFB Screw Press Operator</t>
+        </is>
+      </c>
+      <c r="B201" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C201" s="46" t="n">
         <v>450</v>
       </c>
-      <c r="D201" s="54" t="inlineStr">
+      <c r="D201" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7337,21 +7318,25 @@
         <f>B201*C201</f>
         <v/>
       </c>
-      <c r="F201" s="55" t="inlineStr"/>
+      <c r="F201" s="54" t="inlineStr">
+        <is>
+          <t>MC control, filtrate routing</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="10" t="inlineStr">
         <is>
-          <t>S1 — OPDC Conveyor / Press Operator</t>
-        </is>
-      </c>
-      <c r="B202" s="54" t="n">
+          <t>S1 — OPDC Line Operator (shredder + hammer mill)</t>
+        </is>
+      </c>
+      <c r="B202" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C202" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D202" s="54" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="D202" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7360,75 +7345,71 @@
         <f>B202*C202</f>
         <v/>
       </c>
-      <c r="F202" s="55" t="inlineStr"/>
+      <c r="F202" s="54" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t>S1 — POS Decanter Operator</t>
-        </is>
-      </c>
-      <c r="B203" s="54" t="n">
-        <v>1</v>
+          <t>S1 — OPDC Conveyor / Press Operator</t>
+        </is>
+      </c>
+      <c r="B203" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="C203" s="46" t="n">
-        <v>550</v>
-      </c>
-      <c r="D203" s="54" t="inlineStr">
-        <is>
-          <t>day</t>
+        <v>400</v>
+      </c>
+      <c r="D203" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
         </is>
       </c>
       <c r="E203" s="22">
         <f>B203*C203</f>
         <v/>
       </c>
-      <c r="F203" s="55" t="inlineStr">
-        <is>
-          <t>Skilled: centrifuge operation + Fe gate sampling</t>
-        </is>
-      </c>
+      <c r="F203" s="54" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="10" t="inlineStr">
         <is>
-          <t>S1 — Wheel Loader Operator (EFB/OPDC feed)</t>
-        </is>
-      </c>
-      <c r="B204" s="54" t="n">
-        <v>2</v>
+          <t>S1 — POS Decanter Operator</t>
+        </is>
+      </c>
+      <c r="B204" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="C204" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D204" s="54" t="inlineStr">
-        <is>
-          <t>2-shift</t>
+        <v>550</v>
+      </c>
+      <c r="D204" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
         </is>
       </c>
       <c r="E204" s="22">
         <f>B204*C204</f>
         <v/>
       </c>
-      <c r="F204" s="55" t="inlineStr">
-        <is>
-          <t>Komatsu WA100</t>
+      <c r="F204" s="54" t="inlineStr">
+        <is>
+          <t>Skilled: centrifuge operation + Fe gate sampling</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="10" t="inlineStr">
         <is>
-          <t>S1 — Dump Truck Driver (mill to S1)</t>
-        </is>
-      </c>
-      <c r="B205" s="54" t="n">
+          <t>S1 — Wheel Loader Operator (EFB/OPDC feed)</t>
+        </is>
+      </c>
+      <c r="B205" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C205" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D205" s="54" t="inlineStr">
+        <v>500</v>
+      </c>
+      <c r="D205" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7437,25 +7418,25 @@
         <f>B205*C205</f>
         <v/>
       </c>
-      <c r="F205" s="55" t="inlineStr">
-        <is>
-          <t>2x 10t dump trucks</t>
+      <c r="F205" s="54" t="inlineStr">
+        <is>
+          <t>Komatsu WA100</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="10" t="inlineStr">
         <is>
-          <t>S2 — Chemical Dosing Operator</t>
-        </is>
-      </c>
-      <c r="B206" s="54" t="n">
+          <t>S1 — Dump Truck Driver (mill to S1)</t>
+        </is>
+      </c>
+      <c r="B206" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C206" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D206" s="54" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="D206" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7464,25 +7445,25 @@
         <f>B206*C206</f>
         <v/>
       </c>
-      <c r="F206" s="55" t="inlineStr">
-        <is>
-          <t>PKSA/chemical mixing, pH monitoring</t>
+      <c r="F206" s="54" t="inlineStr">
+        <is>
+          <t>2x 10t dump trucks</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="10" t="inlineStr">
         <is>
-          <t>S2 — Neutralisation Bay Attendant</t>
-        </is>
-      </c>
-      <c r="B207" s="54" t="n">
+          <t>S2 — Chemical Dosing Operator</t>
+        </is>
+      </c>
+      <c r="B207" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C207" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D207" s="54" t="inlineStr">
+        <v>500</v>
+      </c>
+      <c r="D207" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7491,106 +7472,106 @@
         <f>B207*C207</f>
         <v/>
       </c>
-      <c r="F207" s="55" t="inlineStr">
-        <is>
-          <t>Turnings at 8-12hr and 16-20hr</t>
+      <c r="F207" s="54" t="inlineStr">
+        <is>
+          <t>PKSA/chemical mixing, pH monitoring</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
         <is>
-          <t>S3 — Biological Inoculation Technician</t>
-        </is>
-      </c>
-      <c r="B208" s="54" t="n">
-        <v>1</v>
+          <t>S2 — Neutralisation Bay Attendant</t>
+        </is>
+      </c>
+      <c r="B208" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="C208" s="46" t="n">
-        <v>600</v>
-      </c>
-      <c r="D208" s="54" t="inlineStr">
-        <is>
-          <t>day</t>
+        <v>400</v>
+      </c>
+      <c r="D208" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
         </is>
       </c>
       <c r="E208" s="22">
         <f>B208*C208</f>
         <v/>
       </c>
-      <c r="F208" s="55" t="inlineStr">
-        <is>
-          <t>Consortium preparation, spray application</t>
+      <c r="F208" s="54" t="inlineStr">
+        <is>
+          <t>Turnings at 8-12hr and 16-20hr</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="10" t="inlineStr">
         <is>
-          <t>S3 — Composting / Windrow Operator</t>
-        </is>
-      </c>
-      <c r="B209" s="54" t="n">
-        <v>2</v>
+          <t>S3 — Biological Inoculation Technician</t>
+        </is>
+      </c>
+      <c r="B209" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="C209" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D209" s="54" t="inlineStr">
-        <is>
-          <t>2-shift</t>
+        <v>600</v>
+      </c>
+      <c r="D209" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
         </is>
       </c>
       <c r="E209" s="22">
         <f>B209*C209</f>
         <v/>
       </c>
-      <c r="F209" s="55" t="inlineStr">
-        <is>
-          <t>Windrow turner + aeration monitoring</t>
+      <c r="F209" s="54" t="inlineStr">
+        <is>
+          <t>Consortium preparation, spray application</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="10" t="inlineStr">
         <is>
-          <t>S3 — Bobcat Operator (substrate handling)</t>
-        </is>
-      </c>
-      <c r="B210" s="54" t="n">
-        <v>1</v>
+          <t>S3 — Composting / Windrow Operator</t>
+        </is>
+      </c>
+      <c r="B210" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="C210" s="46" t="n">
         <v>450</v>
       </c>
-      <c r="D210" s="54" t="inlineStr">
-        <is>
-          <t>day</t>
+      <c r="D210" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
         </is>
       </c>
       <c r="E210" s="22">
         <f>B210*C210</f>
         <v/>
       </c>
-      <c r="F210" s="55" t="inlineStr">
-        <is>
-          <t>S650 skid-steer</t>
+      <c r="F210" s="54" t="inlineStr">
+        <is>
+          <t>Windrow turner + aeration monitoring</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="10" t="inlineStr">
         <is>
-          <t>S4 — Greenhouse Supervisor</t>
-        </is>
-      </c>
-      <c r="B211" s="54" t="n">
+          <t>S3 — Bobcat Operator (substrate handling)</t>
+        </is>
+      </c>
+      <c r="B211" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C211" s="46" t="n">
-        <v>900</v>
-      </c>
-      <c r="D211" s="54" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="D211" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -7599,52 +7580,52 @@
         <f>B211*C211</f>
         <v/>
       </c>
-      <c r="F211" s="55" t="inlineStr">
-        <is>
-          <t>Overall BSF rearing management</t>
+      <c r="F211" s="54" t="inlineStr">
+        <is>
+          <t>S650 skid-steer</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
         <is>
-          <t>S4 — BSF Tray Attendant (feeding + monitoring)</t>
-        </is>
-      </c>
-      <c r="B212" s="54" t="n">
-        <v>8</v>
+          <t>S4 — Greenhouse Supervisor</t>
+        </is>
+      </c>
+      <c r="B212" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="C212" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D212" s="54" t="inlineStr">
-        <is>
-          <t>2-shift</t>
+        <v>900</v>
+      </c>
+      <c r="D212" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
         </is>
       </c>
       <c r="E212" s="22">
         <f>B212*C212</f>
         <v/>
       </c>
-      <c r="F212" s="55" t="inlineStr">
-        <is>
-          <t>4 per shift, 5000m2 per attendant</t>
+      <c r="F212" s="54" t="inlineStr">
+        <is>
+          <t>Overall BSF rearing management</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="10" t="inlineStr">
         <is>
-          <t>S4 — BSF Neonate Nursery Technician</t>
-        </is>
-      </c>
-      <c r="B213" s="54" t="n">
-        <v>2</v>
+          <t>S4 — BSF Tray Attendant (feeding + monitoring)</t>
+        </is>
+      </c>
+      <c r="B213" s="53" t="n">
+        <v>8</v>
       </c>
       <c r="C213" s="46" t="n">
-        <v>550</v>
-      </c>
-      <c r="D213" s="54" t="inlineStr">
+        <v>400</v>
+      </c>
+      <c r="D213" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7653,79 +7634,79 @@
         <f>B213*C213</f>
         <v/>
       </c>
-      <c r="F213" s="55" t="inlineStr">
-        <is>
-          <t>Colony management, egg collection</t>
+      <c r="F213" s="54" t="inlineStr">
+        <is>
+          <t>4 per shift, 5000m2 per attendant</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="10" t="inlineStr">
         <is>
-          <t>S4 — Greenhouse Climate / IoT Technician</t>
-        </is>
-      </c>
-      <c r="B214" s="54" t="n">
-        <v>1</v>
+          <t>S4 — BSF Neonate Nursery Technician</t>
+        </is>
+      </c>
+      <c r="B214" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="C214" s="46" t="n">
-        <v>700</v>
-      </c>
-      <c r="D214" s="54" t="inlineStr">
-        <is>
-          <t>day</t>
+        <v>550</v>
+      </c>
+      <c r="D214" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
         </is>
       </c>
       <c r="E214" s="22">
         <f>B214*C214</f>
         <v/>
       </c>
-      <c r="F214" s="55" t="inlineStr">
-        <is>
-          <t>SCADA/PLC, sensor maintenance</t>
+      <c r="F214" s="54" t="inlineStr">
+        <is>
+          <t>Colony management, egg collection</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="10" t="inlineStr">
         <is>
-          <t>S4 — Bobcat Operator (greenhouse internal)</t>
-        </is>
-      </c>
-      <c r="B215" s="54" t="n">
-        <v>2</v>
+          <t>S4 — Greenhouse Climate / IoT Technician</t>
+        </is>
+      </c>
+      <c r="B215" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="C215" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D215" s="54" t="inlineStr">
-        <is>
-          <t>2-shift</t>
+        <v>700</v>
+      </c>
+      <c r="D215" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
         </is>
       </c>
       <c r="E215" s="22">
         <f>B215*C215</f>
         <v/>
       </c>
-      <c r="F215" s="55" t="inlineStr">
-        <is>
-          <t>S450, substrate + frass movement</t>
+      <c r="F215" s="54" t="inlineStr">
+        <is>
+          <t>SCADA/PLC, sensor maintenance</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
         <is>
-          <t>S4 — Forklift Operator (greenhouse)</t>
-        </is>
-      </c>
-      <c r="B216" s="54" t="n">
+          <t>S4 — Bobcat Operator (greenhouse internal)</t>
+        </is>
+      </c>
+      <c r="B216" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C216" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D216" s="54" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="D216" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7734,25 +7715,25 @@
         <f>B216*C216</f>
         <v/>
       </c>
-      <c r="F216" s="55" t="inlineStr">
-        <is>
-          <t>1.5t electric forklifts</t>
+      <c r="F216" s="54" t="inlineStr">
+        <is>
+          <t>S450, substrate + frass movement</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="10" t="inlineStr">
         <is>
-          <t>S5A — Frass Screening / Bagging Operator</t>
-        </is>
-      </c>
-      <c r="B217" s="54" t="n">
+          <t>S4 — Forklift Operator (greenhouse)</t>
+        </is>
+      </c>
+      <c r="B217" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C217" s="46" t="n">
         <v>400</v>
       </c>
-      <c r="D217" s="54" t="inlineStr">
+      <c r="D217" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7761,21 +7742,25 @@
         <f>B217*C217</f>
         <v/>
       </c>
-      <c r="F217" s="55" t="inlineStr"/>
+      <c r="F217" s="54" t="inlineStr">
+        <is>
+          <t>1.5t electric forklifts</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="10" t="inlineStr">
         <is>
-          <t>S5B — Larvae Separation Operator</t>
-        </is>
-      </c>
-      <c r="B218" s="54" t="n">
+          <t>S5A — Frass Screening / Bagging Operator</t>
+        </is>
+      </c>
+      <c r="B218" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C218" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D218" s="54" t="inlineStr">
+        <v>400</v>
+      </c>
+      <c r="D218" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7784,25 +7769,21 @@
         <f>B218*C218</f>
         <v/>
       </c>
-      <c r="F218" s="55" t="inlineStr">
-        <is>
-          <t>Vibrating separator + thermal</t>
-        </is>
-      </c>
+      <c r="F218" s="54" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="10" t="inlineStr">
         <is>
-          <t>S5B — Oil Press / Dryer Operator</t>
-        </is>
-      </c>
-      <c r="B219" s="54" t="n">
+          <t>S5B — Larvae Separation Operator</t>
+        </is>
+      </c>
+      <c r="B219" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C219" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D219" s="54" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="D219" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7811,25 +7792,25 @@
         <f>B219*C219</f>
         <v/>
       </c>
-      <c r="F219" s="55" t="inlineStr">
-        <is>
-          <t>Screw press + belt dryer</t>
+      <c r="F219" s="54" t="inlineStr">
+        <is>
+          <t>Vibrating separator + thermal</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
         <is>
-          <t>Warehouse — Forklift Operator</t>
-        </is>
-      </c>
-      <c r="B220" s="54" t="n">
+          <t>S5B — Oil Press / Dryer Operator</t>
+        </is>
+      </c>
+      <c r="B220" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C220" s="46" t="n">
-        <v>400</v>
-      </c>
-      <c r="D220" s="54" t="inlineStr">
+        <v>500</v>
+      </c>
+      <c r="D220" s="53" t="inlineStr">
         <is>
           <t>2-shift</t>
         </is>
@@ -7838,52 +7819,52 @@
         <f>B220*C220</f>
         <v/>
       </c>
-      <c r="F220" s="55" t="inlineStr">
-        <is>
-          <t>3t diesel forklift</t>
+      <c r="F220" s="54" t="inlineStr">
+        <is>
+          <t>Screw press + belt dryer</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="10" t="inlineStr">
         <is>
-          <t>Warehouse — Storeman / Inventory</t>
-        </is>
-      </c>
-      <c r="B221" s="54" t="n">
-        <v>1</v>
+          <t>Warehouse — Forklift Operator</t>
+        </is>
+      </c>
+      <c r="B221" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="C221" s="46" t="n">
-        <v>450</v>
-      </c>
-      <c r="D221" s="54" t="inlineStr">
-        <is>
-          <t>day</t>
+        <v>400</v>
+      </c>
+      <c r="D221" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
         </is>
       </c>
       <c r="E221" s="22">
         <f>B221*C221</f>
         <v/>
       </c>
-      <c r="F221" s="55" t="inlineStr">
-        <is>
-          <t>Stock control, dispatch</t>
+      <c r="F221" s="54" t="inlineStr">
+        <is>
+          <t>3t diesel forklift</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="10" t="inlineStr">
         <is>
-          <t>Logistics — Flatbed Truck Driver</t>
-        </is>
-      </c>
-      <c r="B222" s="54" t="n">
+          <t>Warehouse — Storeman / Inventory</t>
+        </is>
+      </c>
+      <c r="B222" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C222" s="46" t="n">
         <v>450</v>
       </c>
-      <c r="D222" s="54" t="inlineStr">
+      <c r="D222" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -7892,25 +7873,25 @@
         <f>B222*C222</f>
         <v/>
       </c>
-      <c r="F222" s="55" t="inlineStr">
-        <is>
-          <t>Product delivery</t>
+      <c r="F222" s="54" t="inlineStr">
+        <is>
+          <t>Stock control, dispatch</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="10" t="inlineStr">
         <is>
-          <t>Logistics — Tanker Truck Driver</t>
-        </is>
-      </c>
-      <c r="B223" s="54" t="n">
+          <t>Logistics — Flatbed Truck Driver</t>
+        </is>
+      </c>
+      <c r="B223" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C223" s="46" t="n">
         <v>450</v>
       </c>
-      <c r="D223" s="54" t="inlineStr">
+      <c r="D223" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -7919,25 +7900,25 @@
         <f>B223*C223</f>
         <v/>
       </c>
-      <c r="F223" s="55" t="inlineStr">
-        <is>
-          <t>Water/POME</t>
+      <c r="F223" s="54" t="inlineStr">
+        <is>
+          <t>Product delivery</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="10" t="inlineStr">
         <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="B224" s="54" t="n">
+          <t>Logistics — Tanker Truck Driver</t>
+        </is>
+      </c>
+      <c r="B224" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C224" s="46" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D224" s="54" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="D224" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -7946,25 +7927,25 @@
         <f>B224*C224</f>
         <v/>
       </c>
-      <c r="F224" s="55" t="inlineStr">
-        <is>
-          <t>Overall plant management</t>
+      <c r="F224" s="54" t="inlineStr">
+        <is>
+          <t>Water/POME</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="10" t="inlineStr">
         <is>
-          <t>Production Supervisor (S1-S3)</t>
-        </is>
-      </c>
-      <c r="B225" s="54" t="n">
+          <t>Site Manager</t>
+        </is>
+      </c>
+      <c r="B225" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C225" s="46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D225" s="54" t="inlineStr">
+        <v>1500</v>
+      </c>
+      <c r="D225" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -7973,25 +7954,25 @@
         <f>B225*C225</f>
         <v/>
       </c>
-      <c r="F225" s="55" t="inlineStr">
-        <is>
-          <t>Preprocessing + treatment</t>
+      <c r="F225" s="54" t="inlineStr">
+        <is>
+          <t>Overall plant management</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="10" t="inlineStr">
         <is>
-          <t>Quality Control / Lab Technician</t>
-        </is>
-      </c>
-      <c r="B226" s="54" t="n">
-        <v>2</v>
+          <t>Production Supervisor (S1-S3)</t>
+        </is>
+      </c>
+      <c r="B226" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="C226" s="46" t="n">
-        <v>650</v>
-      </c>
-      <c r="D226" s="54" t="inlineStr">
+        <v>1000</v>
+      </c>
+      <c r="D226" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -8000,25 +7981,25 @@
         <f>B226*C226</f>
         <v/>
       </c>
-      <c r="F226" s="55" t="inlineStr">
-        <is>
-          <t>pH, MC, ICP-OES, sampling</t>
+      <c r="F226" s="54" t="inlineStr">
+        <is>
+          <t>Preprocessing + treatment</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="10" t="inlineStr">
         <is>
-          <t>Maintenance Technician (mechanical)</t>
-        </is>
-      </c>
-      <c r="B227" s="54" t="n">
+          <t>Quality Control / Lab Technician</t>
+        </is>
+      </c>
+      <c r="B227" s="53" t="n">
         <v>2</v>
       </c>
       <c r="C227" s="46" t="n">
-        <v>600</v>
-      </c>
-      <c r="D227" s="54" t="inlineStr">
+        <v>650</v>
+      </c>
+      <c r="D227" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -8027,25 +8008,25 @@
         <f>B227*C227</f>
         <v/>
       </c>
-      <c r="F227" s="55" t="inlineStr">
-        <is>
-          <t>All mechanical equipment</t>
+      <c r="F227" s="54" t="inlineStr">
+        <is>
+          <t>pH, MC, ICP-OES, sampling</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Maintenance Technician (electrical/IoT)</t>
-        </is>
-      </c>
-      <c r="B228" s="54" t="n">
-        <v>1</v>
+          <t>Maintenance Technician (mechanical)</t>
+        </is>
+      </c>
+      <c r="B228" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="C228" s="46" t="n">
-        <v>650</v>
-      </c>
-      <c r="D228" s="54" t="inlineStr">
+        <v>600</v>
+      </c>
+      <c r="D228" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -8054,25 +8035,25 @@
         <f>B228*C228</f>
         <v/>
       </c>
-      <c r="F228" s="55" t="inlineStr">
-        <is>
-          <t>Electrical, sensors, PLC</t>
+      <c r="F228" s="54" t="inlineStr">
+        <is>
+          <t>All mechanical equipment</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>HSE Officer</t>
-        </is>
-      </c>
-      <c r="B229" s="54" t="n">
+          <t>Maintenance Technician (electrical/IoT)</t>
+        </is>
+      </c>
+      <c r="B229" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C229" s="46" t="n">
-        <v>700</v>
-      </c>
-      <c r="D229" s="54" t="inlineStr">
+        <v>650</v>
+      </c>
+      <c r="D229" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -8081,25 +8062,25 @@
         <f>B229*C229</f>
         <v/>
       </c>
-      <c r="F229" s="55" t="inlineStr">
-        <is>
-          <t>Safety, PPE, NaOH handling</t>
+      <c r="F229" s="54" t="inlineStr">
+        <is>
+          <t>Electrical, sensors, PLC</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Admin / Finance</t>
-        </is>
-      </c>
-      <c r="B230" s="54" t="n">
-        <v>2</v>
+          <t>HSE Officer</t>
+        </is>
+      </c>
+      <c r="B230" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="C230" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D230" s="54" t="inlineStr">
+        <v>700</v>
+      </c>
+      <c r="D230" s="53" t="inlineStr">
         <is>
           <t>day</t>
         </is>
@@ -8108,371 +8089,398 @@
         <f>B230*C230</f>
         <v/>
       </c>
-      <c r="F230" s="55" t="inlineStr"/>
+      <c r="F230" s="54" t="inlineStr">
+        <is>
+          <t>Safety, PPE, NaOH handling</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>Security (gate + night)</t>
-        </is>
-      </c>
-      <c r="B231" s="54" t="n">
-        <v>3</v>
+          <t>Admin / Finance</t>
+        </is>
+      </c>
+      <c r="B231" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="C231" s="46" t="n">
-        <v>350</v>
-      </c>
-      <c r="D231" s="54" t="inlineStr">
-        <is>
-          <t>3-shift</t>
+        <v>500</v>
+      </c>
+      <c r="D231" s="53" t="inlineStr">
+        <is>
+          <t>day</t>
         </is>
       </c>
       <c r="E231" s="22">
         <f>B231*C231</f>
         <v/>
       </c>
-      <c r="F231" s="55" t="inlineStr">
-        <is>
-          <t>24/7 coverage</t>
-        </is>
-      </c>
+      <c r="F231" s="54" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="10" t="inlineStr">
         <is>
-          <t>Cleaner / General Labour</t>
-        </is>
-      </c>
-      <c r="B232" s="54" t="n">
-        <v>4</v>
+          <t>Security (gate + night)</t>
+        </is>
+      </c>
+      <c r="B232" s="53" t="n">
+        <v>3</v>
       </c>
       <c r="C232" s="46" t="n">
         <v>350</v>
       </c>
-      <c r="D232" s="54" t="inlineStr">
-        <is>
-          <t>2-shift</t>
+      <c r="D232" s="53" t="inlineStr">
+        <is>
+          <t>3-shift</t>
         </is>
       </c>
       <c r="E232" s="22">
         <f>B232*C232</f>
         <v/>
       </c>
-      <c r="F232" s="55" t="inlineStr">
+      <c r="F232" s="54" t="inlineStr">
+        <is>
+          <t>24/7 coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t>Cleaner / General Labour</t>
+        </is>
+      </c>
+      <c r="B233" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C233" s="46" t="n">
+        <v>350</v>
+      </c>
+      <c r="D233" s="53" t="inlineStr">
+        <is>
+          <t>2-shift</t>
+        </is>
+      </c>
+      <c r="E233" s="22">
+        <f>B233*C233</f>
+        <v/>
+      </c>
+      <c r="F233" s="54" t="inlineStr">
         <is>
           <t>Site-wide</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="15" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="15" t="inlineStr">
         <is>
           <t>TOTAL STAFFING</t>
         </is>
       </c>
-      <c r="B233" s="56">
-        <f>SUM(B198:B232)</f>
-        <v/>
-      </c>
-      <c r="E233" s="51">
-        <f>SUM(E198:E232)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="7" t="inlineStr">
+      <c r="B234" s="55">
+        <f>SUM(B199:B233)</f>
+        <v/>
+      </c>
+      <c r="E234" s="51">
+        <f>SUM(E199:E233)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
         <is>
           <t>ANNUAL LABOUR COST (x12 months)</t>
         </is>
       </c>
-      <c r="E234" s="22">
-        <f>E233*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="3" t="inlineStr">
+      <c r="E235" s="22">
+        <f>E234*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
         <is>
           <t>TOTAL CAPEX SUMMARY</t>
         </is>
       </c>
-      <c r="B236" s="3" t="n"/>
-      <c r="C236" s="3" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="38" t="inlineStr">
+      <c r="B237" s="3" t="n"/>
+      <c r="C237" s="3" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="38" t="inlineStr">
         <is>
           <t>TOTAL CAPEX</t>
         </is>
       </c>
-      <c r="B237" s="51">
-        <f>IFERROR(SUM(B5:B236),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="3" t="inlineStr">
+      <c r="B238" s="51">
+        <f>IFERROR(SUM(B5:B237),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
         <is>
           <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
         </is>
       </c>
-      <c r="B239" s="3" t="n"/>
-      <c r="C239" s="3" t="n"/>
-      <c r="D239" s="3" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="9" t="inlineStr">
+      <c r="B240" s="3" t="n"/>
+      <c r="C240" s="3" t="n"/>
+      <c r="D240" s="3" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="inlineStr">
         <is>
           <t>Cost Item</t>
         </is>
       </c>
-      <c r="B240" s="9" t="inlineStr">
+      <c r="B241" s="9" t="inlineStr">
         <is>
           <t>Monthly Cost (USD)</t>
         </is>
       </c>
-      <c r="C240" s="9" t="inlineStr">
+      <c r="C241" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="10" t="inlineStr">
-        <is>
-          <t>Chemical Treatment</t>
-        </is>
-      </c>
-      <c r="B241" s="22">
-        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 2</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="10" t="inlineStr">
         <is>
-          <t>Biological Treatment</t>
+          <t>Chemical Treatment</t>
         </is>
       </c>
       <c r="B242" s="22">
-        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
+        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
         <v/>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>From Stage 3</t>
+          <t>From Stage 2</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
         <is>
-          <t>BSF Neonates</t>
+          <t>Biological Treatment</t>
         </is>
       </c>
       <c r="B243" s="22">
-        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
+        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
         <v/>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>From Stage 4</t>
+          <t>From Stage 3</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="10" t="inlineStr">
         <is>
-          <t>Processing (S5B)</t>
+          <t>BSF Neonates</t>
         </is>
       </c>
       <c r="B244" s="22">
-        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
+        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
         <v/>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>From Stage 5B</t>
+          <t>From Stage 4</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="10" t="inlineStr">
         <is>
-          <t>Energy / Utilities</t>
+          <t>Processing (S5B)</t>
         </is>
       </c>
       <c r="B245" s="22">
-        <f>IFERROR(S1_Preprocessing!B30,0)</f>
+        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
         <v/>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>From Stage 1</t>
+          <t>From Stage 5B</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="10" t="inlineStr">
         <is>
-          <t>Labour (full staffing)</t>
+          <t>Energy / Utilities</t>
         </is>
       </c>
       <c r="B246" s="22">
-        <f>E233</f>
+        <f>IFERROR(S1_Preprocessing!B30,0)</f>
         <v/>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>67 staff — see staffing section row 233</t>
+          <t>From Stage 1</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
         <is>
-          <t>Maintenance (2% CAPEX/month)</t>
+          <t>Labour (full staffing)</t>
         </is>
       </c>
       <c r="B247" s="22">
-        <f>IFERROR(B237*0.02/12,0)</f>
+        <f>E234</f>
         <v/>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Industry standard</t>
+          <t>67 staff — see staffing section row 234</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="10" t="inlineStr">
         <is>
-          <t>Quality Control / Lab</t>
-        </is>
-      </c>
-      <c r="B248" s="46" t="n">
-        <v>2000</v>
+          <t>Maintenance (2% CAPEX/month)</t>
+        </is>
+      </c>
+      <c r="B248" s="22">
+        <f>IFERROR(B238*0.02/12,0)</f>
+        <v/>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Monthly QC testing</t>
+          <t>Industry standard</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="10" t="inlineStr">
         <is>
+          <t>Quality Control / Lab</t>
+        </is>
+      </c>
+      <c r="B249" s="46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Monthly QC testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
+        <is>
           <t>Transport / Logistics</t>
         </is>
       </c>
-      <c r="B249" s="46" t="n">
+      <c r="B250" s="46" t="n">
         <v>3000</v>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>Product distribution</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="38" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="38" t="inlineStr">
         <is>
           <t>TOTAL MONTHLY OPEX</t>
         </is>
       </c>
-      <c r="B250" s="52">
-        <f>IFERROR(SUM(B241:B249),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="inlineStr">
+      <c r="B251" s="52">
+        <f>IFERROR(SUM(B242:B250),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
         <is>
           <t>PAYBACK &amp; NPV ANALYSIS</t>
         </is>
       </c>
-      <c r="B252" s="3" t="n"/>
-      <c r="C252" s="3" t="n"/>
-      <c r="D252" s="3" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="4" t="inlineStr">
-        <is>
-          <t>Total CAPEX</t>
-        </is>
-      </c>
-      <c r="B253" s="22">
-        <f>B237</f>
-        <v/>
-      </c>
+      <c r="B253" s="3" t="n"/>
+      <c r="C253" s="3" t="n"/>
+      <c r="D253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
+          <t>Total CAPEX</t>
+        </is>
+      </c>
+      <c r="B254" s="22">
+        <f>B238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
           <t>Monthly Gross Profit</t>
         </is>
       </c>
-      <c r="B254" s="22">
-        <f>IFERROR(Summary_Dashboard!B24-B250,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="38" t="inlineStr">
+      <c r="B255" s="22">
+        <f>IFERROR(Summary_Dashboard!B24-B251,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="38" t="inlineStr">
         <is>
           <t>Payback Period (months)</t>
         </is>
       </c>
-      <c r="B255" s="42">
-        <f>IFERROR(B253/B254,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="4" t="inlineStr">
+      <c r="B256" s="42">
+        <f>IFERROR(B254/B255,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
         <is>
           <t>Payback Period (years)</t>
         </is>
       </c>
-      <c r="B256" s="13">
-        <f>IFERROR(B255/12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="4" t="inlineStr">
-        <is>
-          <t>IRR Discount Rate (user-adjustable)</t>
-        </is>
-      </c>
-      <c r="B258" s="57" t="n">
-        <v>0.12</v>
+      <c r="B257" s="13">
+        <f>IFERROR(B256/12,0)</f>
+        <v/>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
+          <t>IRR Discount Rate (user-adjustable)</t>
+        </is>
+      </c>
+      <c r="B259" s="56" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
           <t>Annual Net Cash Flow</t>
         </is>
       </c>
-      <c r="B259" s="22">
-        <f>IFERROR(B254*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="7" t="inlineStr">
+      <c r="B260" s="22">
+        <f>IFERROR(B255*12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="7" t="inlineStr">
         <is>
           <t>5-Year NPV (simple estimate)</t>
         </is>
       </c>
-      <c r="B260" s="30">
-        <f>IFERROR(B259/(1+B258)^1+B259/(1+B258)^2+B259/(1+B258)^3+B259/(1+B258)^4+B259/(1+B258)^5-B253,0)</f>
+      <c r="B261" s="30">
+        <f>IFERROR(B260/(1+B259)^1+B260/(1+B259)^2+B260/(1+B259)^3+B260/(1+B259)^4+B260/(1+B259)^5-B254,0)</f>
         <v/>
       </c>
     </row>

--- a/CFI_Master_Excel.xlsx
+++ b/CFI_Master_Excel.xlsx
@@ -4549,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F261"/>
+  <dimension ref="A1:F269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8201,286 +8201,387 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>TOTAL CAPEX SUMMARY</t>
+          <t>DEVELOPMENT &amp; INSTALLATION MARKUPS</t>
         </is>
       </c>
       <c r="B237" s="3" t="n"/>
       <c r="C237" s="3" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="38" t="inlineStr">
-        <is>
-          <t>TOTAL CAPEX</t>
-        </is>
-      </c>
-      <c r="B238" s="51">
-        <f>IFERROR(SUM(B5:B237),0)</f>
-        <v/>
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Equipment / Item</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Cost (USD)</t>
+        </is>
+      </c>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>Equipment CAPEX Subtotal (excl. Process Building EPC)</t>
+        </is>
+      </c>
+      <c r="B239" s="22">
+        <f>IFERROR(SUM(B5:B236)-SUM(B97:B107),0)</f>
+        <v/>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Base for PE/Fixer</t>
+        </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="inlineStr">
+      <c r="A240" s="10" t="inlineStr">
+        <is>
+          <t>Process Engineer / Fixer @ 20% (on equipment, NOT on EPC)</t>
+        </is>
+      </c>
+      <c r="B240" s="22">
+        <f>IFERROR(B239*0.20,0)</f>
+        <v/>
+      </c>
+      <c r="C240" s="10" t="inlineStr">
+        <is>
+          <t>Markup</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="inlineStr">
+        <is>
+          <t>Local EPC @ 15%</t>
+        </is>
+      </c>
+      <c r="B241" s="22">
+        <f>IFERROR((B239+SUM(B97:B107))*0.15,0)</f>
+        <v/>
+      </c>
+      <c r="C241" s="10" t="inlineStr">
+        <is>
+          <t>Markup</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="7" t="inlineStr">
+        <is>
+          <t>Markups Subtotal</t>
+        </is>
+      </c>
+      <c r="B242" s="22">
+        <f>SUM(B240:B241)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX SUMMARY</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n"/>
+      <c r="C244" s="3" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX (all equipment + building + markups)</t>
+        </is>
+      </c>
+      <c r="B245" s="51">
+        <f>IFERROR(SUM(B5:B244),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
         <is>
           <t>MONTHLY OPERATING EXPENDITURE (OPEX)</t>
         </is>
       </c>
-      <c r="B240" s="3" t="n"/>
-      <c r="C240" s="3" t="n"/>
-      <c r="D240" s="3" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="9" t="inlineStr">
+      <c r="B247" s="3" t="n"/>
+      <c r="C247" s="3" t="n"/>
+      <c r="D247" s="3" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="inlineStr">
         <is>
           <t>Cost Item</t>
         </is>
       </c>
-      <c r="B241" s="9" t="inlineStr">
+      <c r="B248" s="9" t="inlineStr">
         <is>
           <t>Monthly Cost (USD)</t>
         </is>
       </c>
-      <c r="C241" s="9" t="inlineStr">
+      <c r="C248" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="10" t="inlineStr">
-        <is>
-          <t>Chemical Treatment</t>
-        </is>
-      </c>
-      <c r="B242" s="22">
-        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="10" t="inlineStr">
-        <is>
-          <t>Biological Treatment</t>
-        </is>
-      </c>
-      <c r="B243" s="22">
-        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
-        <v/>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>BSF Neonates</t>
-        </is>
-      </c>
-      <c r="B244" s="22">
-        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
-        <v/>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>Processing (S5B)</t>
-        </is>
-      </c>
-      <c r="B245" s="22">
-        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
-        <v/>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 5B</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="10" t="inlineStr">
-        <is>
-          <t>Energy / Utilities</t>
-        </is>
-      </c>
-      <c r="B246" s="22">
-        <f>IFERROR(S1_Preprocessing!B30,0)</f>
-        <v/>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>From Stage 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="10" t="inlineStr">
-        <is>
-          <t>Labour (full staffing)</t>
-        </is>
-      </c>
-      <c r="B247" s="22">
-        <f>E234</f>
-        <v/>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>67 staff — see staffing section row 234</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="10" t="inlineStr">
-        <is>
-          <t>Maintenance (2% CAPEX/month)</t>
-        </is>
-      </c>
-      <c r="B248" s="22">
-        <f>IFERROR(B238*0.02/12,0)</f>
-        <v/>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>Industry standard</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="10" t="inlineStr">
         <is>
-          <t>Quality Control / Lab</t>
-        </is>
-      </c>
-      <c r="B249" s="46" t="n">
-        <v>2000</v>
+          <t>Chemical Treatment</t>
+        </is>
+      </c>
+      <c r="B249" s="22">
+        <f>IFERROR(S2_Chemical_Treatment!B33,0)</f>
+        <v/>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Monthly QC testing</t>
+          <t>From Stage 2</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="10" t="inlineStr">
         <is>
+          <t>Biological Treatment</t>
+        </is>
+      </c>
+      <c r="B250" s="22">
+        <f>IFERROR(S3_Biological_Treatment!B33,0)</f>
+        <v/>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
+        <is>
+          <t>BSF Neonates</t>
+        </is>
+      </c>
+      <c r="B251" s="22">
+        <f>IFERROR(S4_BSF_Rearing!B8,0)</f>
+        <v/>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="inlineStr">
+        <is>
+          <t>Processing (S5B)</t>
+        </is>
+      </c>
+      <c r="B252" s="22">
+        <f>IFERROR(S5B_BSF_Extraction!B29,0)</f>
+        <v/>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="inlineStr">
+        <is>
+          <t>Energy / Utilities</t>
+        </is>
+      </c>
+      <c r="B253" s="22">
+        <f>IFERROR(S1_Preprocessing!B30,0)</f>
+        <v/>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>From Stage 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>Labour (full staffing)</t>
+        </is>
+      </c>
+      <c r="B254" s="22">
+        <f>E234</f>
+        <v/>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>67 staff — see staffing section row 234</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance (2% CAPEX/month)</t>
+        </is>
+      </c>
+      <c r="B255" s="22">
+        <f>IFERROR(B245*0.02/12,0)</f>
+        <v/>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Industry standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
+        <is>
+          <t>Political Risk Insurance @ 2% p.a.</t>
+        </is>
+      </c>
+      <c r="B256" s="22">
+        <f>IFERROR(B245*0.02/12,0)</f>
+        <v/>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>2% annual on total CAPEX, monthly provision</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="inlineStr">
+        <is>
+          <t>Quality Control / Lab</t>
+        </is>
+      </c>
+      <c r="B257" s="46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Monthly QC testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
           <t>Transport / Logistics</t>
         </is>
       </c>
-      <c r="B250" s="46" t="n">
+      <c r="B258" s="46" t="n">
         <v>3000</v>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>Product distribution</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="38" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="38" t="inlineStr">
         <is>
           <t>TOTAL MONTHLY OPEX</t>
         </is>
       </c>
-      <c r="B251" s="52">
-        <f>IFERROR(SUM(B242:B250),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="3" t="inlineStr">
+      <c r="B259" s="52">
+        <f>IFERROR(SUM(B249:B258),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
         <is>
           <t>PAYBACK &amp; NPV ANALYSIS</t>
         </is>
       </c>
-      <c r="B253" s="3" t="n"/>
-      <c r="C253" s="3" t="n"/>
-      <c r="D253" s="3" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="4" t="inlineStr">
+      <c r="B261" s="3" t="n"/>
+      <c r="C261" s="3" t="n"/>
+      <c r="D261" s="3" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>Total CAPEX</t>
         </is>
       </c>
-      <c r="B254" s="22">
-        <f>B238</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="4" t="inlineStr">
+      <c r="B262" s="22">
+        <f>B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
         <is>
           <t>Monthly Gross Profit</t>
         </is>
       </c>
-      <c r="B255" s="22">
-        <f>IFERROR(Summary_Dashboard!B24-B251,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="38" t="inlineStr">
+      <c r="B263" s="22">
+        <f>IFERROR(Summary_Dashboard!B24-B259,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="38" t="inlineStr">
         <is>
           <t>Payback Period (months)</t>
         </is>
       </c>
-      <c r="B256" s="42">
-        <f>IFERROR(B254/B255,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="4" t="inlineStr">
+      <c r="B264" s="42">
+        <f>IFERROR(B262/B263,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
         <is>
           <t>Payback Period (years)</t>
         </is>
       </c>
-      <c r="B257" s="13">
-        <f>IFERROR(B256/12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="4" t="inlineStr">
+      <c r="B265" s="13">
+        <f>IFERROR(B264/12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
         <is>
           <t>IRR Discount Rate (user-adjustable)</t>
         </is>
       </c>
-      <c r="B259" s="56" t="n">
+      <c r="B267" s="56" t="n">
         <v>0.12</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
         <is>
           <t>Annual Net Cash Flow</t>
         </is>
       </c>
-      <c r="B260" s="22">
-        <f>IFERROR(B255*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="7" t="inlineStr">
+      <c r="B268" s="22">
+        <f>IFERROR(B263*12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="7" t="inlineStr">
         <is>
           <t>5-Year NPV (simple estimate)</t>
         </is>
       </c>
-      <c r="B261" s="30">
-        <f>IFERROR(B260/(1+B259)^1+B260/(1+B259)^2+B260/(1+B259)^3+B260/(1+B259)^4+B260/(1+B259)^5-B254,0)</f>
+      <c r="B269" s="30">
+        <f>IFERROR(B268/(1+B267)^1+B268/(1+B267)^2+B268/(1+B267)^3+B268/(1+B267)^4+B268/(1+B267)^5-B262,0)</f>
         <v/>
       </c>
     </row>
